--- a/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Marzo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AA8456E-447B-4145-9F52-D3EEA3206FA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A04A8E0-9970-4EA2-B4F8-02D6CB28D8D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,19 +19,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$N$64</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$F$123</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="146">
   <si>
     <t>consorciobelgrano1640@gmail.com</t>
   </si>
@@ -282,9 +277,6 @@
     <t>SAC</t>
   </si>
   <si>
-    <t>TOTAL SAC</t>
-  </si>
-  <si>
     <t>LUSENSKY, CARLOS</t>
   </si>
   <si>
@@ -339,9 +331,6 @@
     <t>EL MONTO QUE SE PRORRATEA EN LAS UNIDADES FUNCIONALES ES MAYOR AL MONTO QUE SE GASTO YA QUE DE PRORRATEAR EL MONTO GASTADO NO SE ALCANZA A JUNTAR EL DINERO NECESARIO PARA CUBRIR EL 100% DE LOS GASTOS. ESTO SE DEBE A QUE EL LOCAL NO ABONA ESTRICTAMENTE EL 8,09% DE TODA LA LIQUIDACION, SINO QUE ABONA EL 8,09% DE ALGUNOS GASTOS SI Y DE OTROS NO. ES POR ESO MISMO QUE SE DEBE PRORRATEAR UN MONTO MAYOR A LO GASTADO PARA CON LAS UNIDADES FUNCIONALES CON EL OBJETIVO DE A FIN DE CUENTAS SI PODER REACAUDAR LO GASTADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Redondeo </t>
-  </si>
-  <si>
     <t>EXPENSAS EXTRA:</t>
   </si>
   <si>
@@ -367,9 +356,6 @@
   </si>
   <si>
     <t>GASTOS PARTICULARES</t>
-  </si>
-  <si>
-    <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO</t>
   </si>
   <si>
     <t xml:space="preserve">Numero 1859135 Debito automatico </t>
@@ -440,45 +426,15 @@
     </r>
   </si>
   <si>
-    <t>VTO: 17/04</t>
-  </si>
-  <si>
-    <t>Alterini - Jardineria - Mantenimiento 27/02, maceta, rosa china, tierra fertil</t>
-  </si>
-  <si>
-    <t>Servisur - 1 sensor de movimieno - 13 plafones de techo</t>
-  </si>
-  <si>
     <t>Casa Ruan - Compra de materiales electricos</t>
   </si>
   <si>
-    <t>PERÍODO: MARZO</t>
-  </si>
-  <si>
-    <t>Honorarios MARZO</t>
-  </si>
-  <si>
-    <t>Ingreso mes de FEBRERO</t>
-  </si>
-  <si>
     <t>BORRAR A MAURO MARANTE DE MAILS</t>
   </si>
   <si>
-    <t>Renovacion de Wifi y Cable (2 bocas) anual</t>
-  </si>
-  <si>
-    <t>Debito 04/3</t>
-  </si>
-  <si>
-    <t>Fumigacion - Mes de febrero</t>
-  </si>
-  <si>
     <t>Pago mis cuentas 09/03</t>
   </si>
   <si>
-    <t xml:space="preserve">Tofema - Compra de materiales </t>
-  </si>
-  <si>
     <t>Debito 12/03</t>
   </si>
   <si>
@@ -488,22 +444,58 @@
     <t>Pago 20/03</t>
   </si>
   <si>
-    <t>Gustavo Padron contador - Presentacion Balance RPAC</t>
-  </si>
-  <si>
     <t>Fumigacion - Mes de marzo</t>
   </si>
   <si>
-    <t>Destapacion AySa - Pago en efectivo</t>
-  </si>
-  <si>
-    <t>Alterini - Jardineria - Maceta premium, tierra fertil, mantenimiento</t>
-  </si>
-  <si>
-    <t>Se adeuda mes de Marzo</t>
-  </si>
-  <si>
     <t>Articulos de limpieza - Montoya Alejandra - Cif, liquido para pisos, guantes, etc</t>
+  </si>
+  <si>
+    <t>VTO: 15/05</t>
+  </si>
+  <si>
+    <t>PERÍODO: ABRIL</t>
+  </si>
+  <si>
+    <t>Honorarios ABRIL</t>
+  </si>
+  <si>
+    <t>Fumigacion - Mes de ABRIL</t>
+  </si>
+  <si>
+    <t>Se adeuda mes de ABRIL</t>
+  </si>
+  <si>
+    <t>Ingreso mes de marzo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remis Sr. Diego </t>
+  </si>
+  <si>
+    <t>Reemplazo Sr. Diego - Sra Monica</t>
+  </si>
+  <si>
+    <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO - MARZO</t>
+  </si>
+  <si>
+    <t>Energroup - SERVICE DE MANTENIMIENTO PREVENTIVO - ABRIL</t>
+  </si>
+  <si>
+    <t>Distribuidora Barbiero - Lamparas y plafones</t>
+  </si>
+  <si>
+    <t>Casa Ruan - Sensor de movimiento pared</t>
+  </si>
+  <si>
+    <t>Servisur - Colocacion de lamparas, sensores, plafones y programacion de reloj filtro pileta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citro nicolas Hugo -  Pago de franquicia </t>
+  </si>
+  <si>
+    <t>Gastañaga Sebastian - Destabe y encarrilamiento persiana metalica</t>
+  </si>
+  <si>
+    <t>Debito 06/04</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1055,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="212">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
@@ -1245,6 +1237,21 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1313,6 +1320,24 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1322,6 +1347,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1337,12 +1368,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1394,38 +1419,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="13" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1506,9 +1503,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1546,9 +1543,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1581,26 +1578,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1633,26 +1613,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1826,34 +1789,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N131"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N133"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="94"/>
-      <c r="B1" s="145" t="s">
-        <v>91</v>
-      </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="146"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="152" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="152"/>
+      <c r="D1" s="152"/>
+      <c r="E1" s="152"/>
+      <c r="F1" s="153"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="9"/>
       <c r="B2" s="111" t="s">
         <v>0</v>
@@ -1863,7 +1826,7 @@
       <c r="E2" s="111"/>
       <c r="F2" s="112"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="9"/>
       <c r="B3" s="111" t="s">
         <v>61</v>
@@ -1873,7 +1836,7 @@
       <c r="E3" s="111"/>
       <c r="F3" s="112"/>
     </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9"/>
       <c r="B4" s="111" t="s">
         <v>62</v>
@@ -1883,21 +1846,21 @@
       <c r="E4" s="111"/>
       <c r="F4" s="112"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="111" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C5" s="111" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D5" s="111"/>
       <c r="E5" s="111"/>
       <c r="F5" s="112"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>72</v>
       </c>
@@ -1907,7 +1870,7 @@
       <c r="E6" s="111"/>
       <c r="F6" s="112"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="115" t="s">
         <v>71</v>
       </c>
@@ -1917,87 +1880,87 @@
       <c r="E7" s="113"/>
       <c r="F7" s="114"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="81"/>
       <c r="B8" s="81"/>
       <c r="C8" s="81"/>
       <c r="D8" s="81"/>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="81"/>
       <c r="B9" s="81"/>
       <c r="C9" s="81"/>
       <c r="D9" s="81"/>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="81"/>
       <c r="B10" s="81"/>
       <c r="C10" s="81"/>
       <c r="D10" s="81"/>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="81"/>
       <c r="B11" s="81"/>
       <c r="C11" s="81"/>
       <c r="D11" s="81"/>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="81"/>
       <c r="B12" s="81"/>
       <c r="C12" s="81"/>
       <c r="D12" s="81"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="81"/>
       <c r="B13" s="81"/>
       <c r="C13" s="81"/>
       <c r="D13" s="81"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="81"/>
-      <c r="B14" s="149" t="s">
-        <v>124</v>
-      </c>
-      <c r="C14" s="150"/>
-      <c r="D14" s="151"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="156" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="157"/>
+      <c r="D14" s="158"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="81"/>
-      <c r="B15" s="152"/>
-      <c r="C15" s="153"/>
-      <c r="D15" s="154"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="159"/>
+      <c r="C15" s="160"/>
+      <c r="D15" s="161"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="81"/>
-      <c r="B16" s="152"/>
-      <c r="C16" s="153"/>
-      <c r="D16" s="154"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="159"/>
+      <c r="C16" s="160"/>
+      <c r="D16" s="161"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="81"/>
-      <c r="B17" s="155"/>
-      <c r="C17" s="156"/>
-      <c r="D17" s="157"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="162"/>
+      <c r="C17" s="163"/>
+      <c r="D17" s="164"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="81"/>
       <c r="B18" s="81"/>
       <c r="C18" s="81"/>
       <c r="D18" s="81"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="117"/>
       <c r="B19" s="81"/>
       <c r="C19" s="81"/>
       <c r="D19" s="81"/>
     </row>
-    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="81"/>
       <c r="B20" s="81"/>
       <c r="C20" s="81"/>
       <c r="D20" s="81"/>
     </row>
-    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="118" t="s">
         <v>59</v>
       </c>
@@ -2005,27 +1968,27 @@
       <c r="C21" s="120"/>
       <c r="D21" s="121"/>
       <c r="E21" s="87" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="88" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="122" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B22" s="82" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C22" s="82"/>
-      <c r="D22" s="196"/>
+      <c r="D22" s="145"/>
       <c r="E22" s="86"/>
       <c r="F22" s="86"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="122" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B23" s="82"/>
       <c r="C23" s="82"/>
@@ -2041,7 +2004,7 @@
         <v>125868.98015600001</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="122" t="s">
         <v>2</v>
       </c>
@@ -2060,9 +2023,9 @@
       </c>
       <c r="G24" s="36"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="122" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B25" s="82"/>
       <c r="C25" s="82"/>
@@ -2078,7 +2041,7 @@
         <v>3.8022999999999994E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="122"/>
       <c r="B26" s="82"/>
       <c r="C26" s="82"/>
@@ -2092,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="123" t="s">
         <v>3</v>
       </c>
@@ -2119,7 +2082,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="124" t="s">
         <v>82</v>
       </c>
@@ -2138,7 +2101,7 @@
       </c>
       <c r="H28" s="64"/>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="124"/>
       <c r="B29" s="82"/>
       <c r="C29" s="82"/>
@@ -2155,7 +2118,7 @@
       </c>
       <c r="H29" s="64"/>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="124"/>
       <c r="B30" s="82"/>
       <c r="C30" s="82"/>
@@ -2164,7 +2127,7 @@
       <c r="F30" s="4"/>
       <c r="H30" s="64"/>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="124"/>
       <c r="B31" s="82"/>
       <c r="C31" s="82"/>
@@ -2173,9 +2136,9 @@
       <c r="F31" s="4"/>
       <c r="H31" s="64"/>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B32" s="123"/>
       <c r="C32" s="123"/>
@@ -2200,27 +2163,27 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="124" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="B33" s="82"/>
       <c r="C33" s="82"/>
-      <c r="D33" s="107"/>
+      <c r="D33" s="210">
+        <v>84000</v>
+      </c>
       <c r="E33" s="52">
         <f>D33*91.91%</f>
-        <v>0</v>
+        <v>77204.399999999994</v>
       </c>
       <c r="F33" s="52">
         <f>D33*8.09%</f>
-        <v>0</v>
+        <v>6795.6</v>
       </c>
       <c r="H33" s="64"/>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="82" t="s">
-        <v>102</v>
-      </c>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="82"/>
       <c r="B34" s="82"/>
       <c r="C34" s="82"/>
       <c r="D34" s="106"/>
@@ -2234,10 +2197,8 @@
       </c>
       <c r="H34" s="64"/>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="124" t="s">
-        <v>2</v>
-      </c>
+    <row r="35" spans="1:8" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="124"/>
       <c r="B35" s="82"/>
       <c r="C35" s="82"/>
       <c r="D35" s="106"/>
@@ -2251,27 +2212,27 @@
       </c>
       <c r="H35" s="64"/>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="123" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B36" s="123"/>
       <c r="C36" s="123"/>
       <c r="D36" s="35">
         <f>SUM(D29:D35)</f>
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="E36" s="35">
         <f t="shared" ref="E36" si="5">SUM(E29:E35)</f>
-        <v>0</v>
+        <v>77204.399999999994</v>
       </c>
       <c r="F36" s="44">
         <f>E36*8.09%</f>
-        <v>0</v>
+        <v>6245.8359599999994</v>
       </c>
       <c r="H36" s="64"/>
     </row>
-    <row r="37" spans="1:8" ht="0.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="0.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="125"/>
       <c r="B37" s="105"/>
       <c r="C37" s="105"/>
@@ -2280,7 +2241,7 @@
       <c r="F37" s="45"/>
       <c r="H37" s="64"/>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="125"/>
       <c r="B38" s="105"/>
       <c r="C38" s="105"/>
@@ -2289,7 +2250,7 @@
       <c r="F38" s="45"/>
       <c r="H38" s="64"/>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="105"/>
       <c r="B39" s="105"/>
       <c r="C39" s="126"/>
@@ -2298,9 +2259,9 @@
       <c r="F39" s="45"/>
       <c r="H39" s="64"/>
     </row>
-    <row r="40" spans="1:8" ht="1.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" s="123"/>
       <c r="C40" s="123"/>
@@ -2315,9 +2276,9 @@
       </c>
       <c r="H40" s="64"/>
     </row>
-    <row r="41" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="82" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B41" s="82"/>
       <c r="C41" s="105"/>
@@ -2332,9 +2293,9 @@
       <c r="F41" s="52"/>
       <c r="H41" s="64"/>
     </row>
-    <row r="42" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="123" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B42" s="123"/>
       <c r="C42" s="123"/>
@@ -2356,7 +2317,7 @@
       </c>
       <c r="H42" s="64"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="124" t="s">
         <v>4</v>
       </c>
@@ -2367,9 +2328,9 @@
       <c r="F43" s="28"/>
       <c r="H43" s="64"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="124" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B44" s="82"/>
       <c r="C44" s="105"/>
@@ -2386,50 +2347,50 @@
       </c>
       <c r="H44" s="64"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="124" t="s">
         <v>5</v>
       </c>
       <c r="B45" s="82" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C45" s="82"/>
-      <c r="D45" s="39">
-        <f>142643.75+7840+70562.6</f>
-        <v>221046.35</v>
+      <c r="D45" s="209">
+        <f>70013.65+7779.29+142542.82</f>
+        <v>220335.76</v>
       </c>
       <c r="E45" s="52">
         <f>D45*91.91%</f>
-        <v>203163.700285</v>
+        <v>202510.59701599999</v>
       </c>
       <c r="F45" s="52">
         <f>D45*8.09%</f>
-        <v>17882.649715</v>
+        <v>17825.162984000002</v>
       </c>
       <c r="H45" s="64"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="124" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B46" s="105" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="C46" s="82"/>
-      <c r="D46" s="39">
-        <v>695037.24</v>
+      <c r="D46" s="209">
+        <v>689724.49</v>
       </c>
       <c r="E46" s="52">
         <f>D46*91.91%</f>
-        <v>638808.72728399991</v>
+        <v>633925.77875899989</v>
       </c>
       <c r="F46" s="52">
         <f>D46*8.09%</f>
-        <v>56228.512715999997</v>
+        <v>55798.711240999997</v>
       </c>
       <c r="H46" s="64"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="123" t="s">
         <v>6</v>
       </c>
@@ -2437,26 +2398,26 @@
       <c r="C47" s="127"/>
       <c r="D47" s="35">
         <f>SUM(D44:D46)</f>
-        <v>922725.59</v>
+        <v>916702.25</v>
       </c>
       <c r="E47" s="35">
         <f t="shared" ref="E47:F47" si="6">SUM(E44:E46)</f>
-        <v>848077.08976899995</v>
+        <v>842541.03797499987</v>
       </c>
       <c r="F47" s="35">
         <f t="shared" si="6"/>
-        <v>74648.500230999998</v>
+        <v>74161.212025000001</v>
       </c>
       <c r="G47" s="36">
         <f>E47+F47</f>
-        <v>922725.59</v>
+        <v>916702.24999999988</v>
       </c>
       <c r="H47" s="64" t="str">
         <f>IF(D47=G47, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="82" t="s">
         <v>7</v>
       </c>
@@ -2467,13 +2428,13 @@
       <c r="F48" s="4"/>
       <c r="H48" s="64"/>
     </row>
-    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="128" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B49" s="82"/>
       <c r="C49" s="82"/>
-      <c r="D49" s="39">
+      <c r="D49" s="209">
         <v>434000</v>
       </c>
       <c r="E49" s="63">
@@ -2495,9 +2456,9 @@
       </c>
       <c r="J49" s="79"/>
     </row>
-    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="128" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B50" s="82"/>
       <c r="C50" s="82"/>
@@ -2514,7 +2475,7 @@
       <c r="I50" s="79"/>
       <c r="J50" s="79"/>
     </row>
-    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="122" t="s">
         <v>8</v>
       </c>
@@ -2524,1220 +2485,1272 @@
         <v>241100</v>
       </c>
       <c r="E51" s="63">
-        <f t="shared" ref="E51:E55" si="7">D51*91.91%</f>
+        <f t="shared" ref="E51:E56" si="7">D51*91.91%</f>
         <v>221595.00999999998</v>
       </c>
       <c r="F51" s="52">
-        <f t="shared" ref="F51:F55" si="8">D51*8.09%</f>
+        <f t="shared" ref="F51:F56" si="8">D51*8.09%</f>
         <v>19504.990000000002</v>
       </c>
       <c r="G51" s="36">
-        <f t="shared" ref="G51:G65" si="9">D51</f>
+        <f t="shared" ref="G51:G67" si="9">D51</f>
         <v>241100</v>
       </c>
       <c r="H51" s="70">
-        <f t="shared" ref="H51:H65" si="10">E51+F51</f>
+        <f t="shared" ref="H51:H67" si="10">E51+F51</f>
         <v>241099.99999999997</v>
       </c>
       <c r="I51" s="79"/>
       <c r="J51" s="79"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="124" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B52" s="82"/>
       <c r="C52" s="82"/>
-      <c r="D52" s="39">
-        <v>893616.94</v>
+      <c r="D52" s="209">
+        <v>176418</v>
       </c>
       <c r="E52" s="63">
         <f t="shared" si="7"/>
-        <v>821323.32955399982</v>
+        <v>162145.78379999998</v>
       </c>
       <c r="F52" s="52">
         <f t="shared" si="8"/>
-        <v>72293.610445999991</v>
+        <v>14272.216200000001</v>
       </c>
       <c r="G52" s="36">
         <f t="shared" si="9"/>
-        <v>893616.94</v>
+        <v>176418</v>
       </c>
       <c r="H52" s="70">
         <f t="shared" si="10"/>
-        <v>893616.93999999983</v>
+        <v>176417.99999999997</v>
       </c>
       <c r="I52" s="79"/>
       <c r="J52" s="79"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="124" t="s">
+        <v>139</v>
+      </c>
+      <c r="B53" s="82"/>
+      <c r="C53" s="82"/>
+      <c r="D53" s="209">
+        <v>192118.96</v>
+      </c>
+      <c r="E53" s="63">
+        <f t="shared" ref="E53" si="11">D53*91.91%</f>
+        <v>176576.53613599998</v>
+      </c>
+      <c r="F53" s="52">
+        <f t="shared" ref="F53" si="12">D53*8.09%</f>
+        <v>15542.423863999999</v>
+      </c>
+      <c r="G53" s="36">
+        <f t="shared" ref="G53" si="13">D53</f>
+        <v>192118.96</v>
+      </c>
+      <c r="H53" s="70">
+        <f t="shared" ref="H53" si="14">E53+F53</f>
+        <v>192118.96</v>
+      </c>
+      <c r="I53" s="79"/>
+      <c r="J53" s="79"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="B53" s="82" t="s">
-        <v>113</v>
-      </c>
-      <c r="C53" s="82"/>
-      <c r="D53" s="39">
+      <c r="B54" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="C54" s="82"/>
+      <c r="D54" s="39">
         <v>129320</v>
       </c>
-      <c r="E53" s="63">
-        <f>D53*91.91%</f>
+      <c r="E54" s="63">
+        <f>D54*91.91%</f>
         <v>118858.01199999999</v>
       </c>
-      <c r="F53" s="52">
+      <c r="F54" s="52">
         <f t="shared" si="8"/>
         <v>10461.987999999999</v>
       </c>
-      <c r="G53" s="36">
+      <c r="G54" s="36">
         <f t="shared" si="9"/>
         <v>129320</v>
       </c>
-      <c r="H53" s="70">
-        <f>E53+F53</f>
+      <c r="H54" s="70">
+        <f>E54+F54</f>
         <v>129319.99999999999</v>
       </c>
-      <c r="I53" s="79">
-        <f t="shared" ref="I53:I65" si="11">H53-D53</f>
-        <v>0</v>
-      </c>
-      <c r="J53" s="79">
-        <f t="shared" ref="J53:J65" si="12">G53-D53</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="124" t="s">
+      <c r="I54" s="79">
+        <f t="shared" ref="I54:I67" si="15">H54-D54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="79">
+        <f t="shared" ref="J54:J67" si="16">G54-D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="B54" s="105" t="s">
-        <v>134</v>
-      </c>
-      <c r="C54" s="82"/>
-      <c r="D54" s="39">
-        <v>843680.39</v>
-      </c>
-      <c r="E54" s="63">
-        <f t="shared" si="7"/>
-        <v>775426.64644899999</v>
-      </c>
-      <c r="F54" s="52">
-        <f t="shared" si="8"/>
-        <v>68253.743551000007</v>
-      </c>
-      <c r="G54" s="36">
-        <f t="shared" si="9"/>
-        <v>843680.39</v>
-      </c>
-      <c r="H54" s="70">
-        <f t="shared" si="10"/>
-        <v>843680.39</v>
-      </c>
-      <c r="I54" s="79">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J54" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="125" t="s">
-        <v>10</v>
-      </c>
       <c r="B55" s="105" t="s">
-        <v>140</v>
-      </c>
-      <c r="C55" s="105"/>
-      <c r="D55" s="39">
-        <v>897000</v>
+        <v>145</v>
+      </c>
+      <c r="C55" s="82"/>
+      <c r="D55" s="209">
+        <v>353513.62</v>
       </c>
       <c r="E55" s="63">
         <f t="shared" si="7"/>
-        <v>824432.7</v>
+        <v>324914.36814199999</v>
       </c>
       <c r="F55" s="52">
         <f t="shared" si="8"/>
-        <v>72567.3</v>
+        <v>28599.251858</v>
       </c>
       <c r="G55" s="36">
         <f t="shared" si="9"/>
-        <v>897000</v>
+        <v>353513.62</v>
       </c>
       <c r="H55" s="70">
         <f t="shared" si="10"/>
-        <v>897000</v>
+        <v>353513.62</v>
       </c>
       <c r="I55" s="79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J55" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="105" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" s="105"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="125" t="s">
+        <v>10</v>
+      </c>
+      <c r="B56" s="105" t="s">
+        <v>127</v>
+      </c>
       <c r="C56" s="105"/>
       <c r="D56" s="39">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="E56" s="63">
-        <f>D56</f>
-        <v>300000</v>
-      </c>
-      <c r="F56" s="52"/>
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="52">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
       <c r="G56" s="36">
         <f t="shared" si="9"/>
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="H56" s="70">
         <f t="shared" si="10"/>
-        <v>300000</v>
-      </c>
-      <c r="I56" s="79"/>
-      <c r="J56" s="79"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="132" t="s">
-        <v>135</v>
-      </c>
-      <c r="B57" s="132"/>
-      <c r="C57" s="132"/>
-      <c r="D57" s="39">
-        <v>56600</v>
+        <v>0</v>
+      </c>
+      <c r="I56" s="79">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="79">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="105" t="s">
+        <v>136</v>
+      </c>
+      <c r="B57" s="105"/>
+      <c r="C57" s="105"/>
+      <c r="D57" s="209">
+        <v>20000</v>
       </c>
       <c r="E57" s="63">
-        <f t="shared" ref="E57:E58" si="13">D57</f>
-        <v>56600</v>
+        <f>D57</f>
+        <v>20000</v>
       </c>
       <c r="F57" s="52"/>
       <c r="G57" s="36">
         <f t="shared" si="9"/>
-        <v>56600</v>
+        <v>20000</v>
       </c>
       <c r="H57" s="70">
         <f t="shared" si="10"/>
+        <v>20000</v>
+      </c>
+      <c r="I57" s="79"/>
+      <c r="J57" s="79"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="B58" s="132"/>
+      <c r="C58" s="132"/>
+      <c r="D58" s="39">
         <v>56600</v>
       </c>
-      <c r="I57" s="79">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="132" t="s">
-        <v>142</v>
-      </c>
-      <c r="B58" s="203"/>
-      <c r="C58" s="204"/>
-      <c r="D58" s="39">
-        <v>58200</v>
-      </c>
       <c r="E58" s="63">
-        <f t="shared" si="13"/>
-        <v>58200</v>
+        <f t="shared" ref="E58:E59" si="17">D58</f>
+        <v>56600</v>
       </c>
       <c r="F58" s="52"/>
       <c r="G58" s="36">
         <f t="shared" si="9"/>
+        <v>56600</v>
+      </c>
+      <c r="H58" s="70">
+        <f t="shared" si="10"/>
+        <v>56600</v>
+      </c>
+      <c r="I58" s="79">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J58" s="79">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="132" t="s">
+        <v>133</v>
+      </c>
+      <c r="B59" s="149"/>
+      <c r="C59" s="150"/>
+      <c r="D59" s="39">
         <v>58200</v>
       </c>
-      <c r="H58" s="70"/>
-      <c r="I58" s="79"/>
-      <c r="J58" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="197" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="133"/>
-      <c r="C59" s="134"/>
-      <c r="D59" s="39">
-        <v>250000</v>
-      </c>
       <c r="E59" s="63">
-        <f>D59</f>
-        <v>250000</v>
+        <f t="shared" si="17"/>
+        <v>58200</v>
       </c>
       <c r="F59" s="52"/>
       <c r="G59" s="36">
         <f t="shared" si="9"/>
-        <v>250000</v>
-      </c>
-      <c r="H59" s="70">
-        <f t="shared" si="10"/>
-        <v>250000</v>
-      </c>
-      <c r="I59" s="79">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+        <v>58200</v>
+      </c>
+      <c r="H59" s="70"/>
+      <c r="I59" s="79"/>
       <c r="J59" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="197" t="s">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="146" t="s">
         <v>144</v>
       </c>
       <c r="B60" s="133"/>
       <c r="C60" s="134"/>
-      <c r="D60" s="39">
-        <v>330000</v>
+      <c r="D60" s="209">
+        <v>160000</v>
       </c>
       <c r="E60" s="63">
         <f>D60</f>
-        <v>330000</v>
+        <v>160000</v>
       </c>
       <c r="F60" s="52"/>
       <c r="G60" s="36">
         <f t="shared" si="9"/>
-        <v>330000</v>
+        <v>160000</v>
       </c>
       <c r="H60" s="70">
         <f t="shared" si="10"/>
-        <v>330000</v>
-      </c>
-      <c r="I60" s="79"/>
+        <v>160000</v>
+      </c>
+      <c r="I60" s="79">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
       <c r="J60" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="206" t="s">
-        <v>143</v>
-      </c>
-      <c r="B61" s="207"/>
-      <c r="C61" s="208"/>
-      <c r="D61" s="39">
-        <v>60000</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="211" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" s="133"/>
+      <c r="C61" s="134"/>
+      <c r="D61" s="209">
+        <v>580000</v>
       </c>
       <c r="E61" s="63">
-        <f t="shared" ref="E61" si="14">D61*91.91%</f>
-        <v>55145.999999999993</v>
-      </c>
-      <c r="F61" s="52">
-        <f t="shared" ref="F61" si="15">D61*8.09%</f>
-        <v>4854</v>
-      </c>
+        <f>D61</f>
+        <v>580000</v>
+      </c>
+      <c r="F61" s="52"/>
       <c r="G61" s="36">
-        <f t="shared" ref="G61" si="16">D61</f>
-        <v>60000</v>
+        <f t="shared" si="9"/>
+        <v>580000</v>
       </c>
       <c r="H61" s="70">
-        <f t="shared" ref="H61" si="17">E61+F61</f>
-        <v>59999.999999999993</v>
+        <f t="shared" si="10"/>
+        <v>580000</v>
       </c>
       <c r="I61" s="79"/>
-      <c r="J61" s="79"/>
-    </row>
-    <row r="62" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="82" t="s">
-        <v>92</v>
-      </c>
-      <c r="B62" s="82"/>
-      <c r="C62" s="82"/>
-      <c r="D62" s="39">
-        <v>10775</v>
+      <c r="J61" s="79">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="146" t="s">
+        <v>140</v>
+      </c>
+      <c r="B62" s="133"/>
+      <c r="C62" s="134"/>
+      <c r="D62" s="209">
+        <v>52724.63</v>
       </c>
       <c r="E62" s="63">
-        <f t="shared" ref="E62:E65" si="18">D62</f>
-        <v>10775</v>
+        <f>D62</f>
+        <v>52724.63</v>
       </c>
       <c r="F62" s="52"/>
       <c r="G62" s="36">
         <f t="shared" si="9"/>
-        <v>10775</v>
+        <v>52724.63</v>
       </c>
       <c r="H62" s="70">
         <f t="shared" si="10"/>
-        <v>10775</v>
-      </c>
-      <c r="I62" s="79">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+        <v>52724.63</v>
+      </c>
+      <c r="I62" s="79"/>
       <c r="J62" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="144" t="s">
-        <v>137</v>
-      </c>
-      <c r="B63" s="129"/>
-      <c r="C63" s="130"/>
-      <c r="D63" s="39">
-        <v>107437.59</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="179" t="s">
+        <v>141</v>
+      </c>
+      <c r="B63" s="180"/>
+      <c r="C63" s="181"/>
+      <c r="D63" s="209">
+        <v>19800</v>
       </c>
       <c r="E63" s="63">
-        <f t="shared" si="18"/>
-        <v>107437.59</v>
-      </c>
-      <c r="F63" s="52"/>
+        <f t="shared" ref="E63" si="18">D63*91.91%</f>
+        <v>18198.179999999997</v>
+      </c>
+      <c r="F63" s="52">
+        <f t="shared" ref="F63" si="19">D63*8.09%</f>
+        <v>1601.82</v>
+      </c>
       <c r="G63" s="36">
-        <f t="shared" si="9"/>
-        <v>107437.59</v>
+        <f t="shared" ref="G63" si="20">D63</f>
+        <v>19800</v>
       </c>
       <c r="H63" s="70">
-        <f t="shared" si="10"/>
-        <v>107437.59</v>
-      </c>
-      <c r="I63" s="79">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J63" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="144" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="129"/>
-      <c r="C64" s="201"/>
-      <c r="D64" s="39">
-        <v>21900</v>
+        <f t="shared" ref="H63" si="21">E63+F63</f>
+        <v>19799.999999999996</v>
+      </c>
+      <c r="I63" s="79"/>
+      <c r="J63" s="79"/>
+    </row>
+    <row r="64" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="82" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="82"/>
+      <c r="C64" s="82"/>
+      <c r="D64" s="209">
+        <v>135000</v>
       </c>
       <c r="E64" s="63">
-        <f t="shared" si="18"/>
-        <v>21900</v>
+        <f t="shared" ref="E64:E67" si="22">D64</f>
+        <v>135000</v>
       </c>
       <c r="F64" s="52"/>
       <c r="G64" s="36">
         <f t="shared" si="9"/>
-        <v>21900</v>
+        <v>135000</v>
       </c>
       <c r="H64" s="70">
         <f t="shared" si="10"/>
-        <v>21900</v>
+        <v>135000</v>
       </c>
       <c r="I64" s="79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J64" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="198" t="s">
-        <v>127</v>
-      </c>
-      <c r="B65" s="199"/>
-      <c r="C65" s="200"/>
-      <c r="D65" s="39">
-        <v>220000</v>
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="82" t="s">
+        <v>91</v>
+      </c>
+      <c r="B65" s="129"/>
+      <c r="C65" s="130"/>
+      <c r="D65" s="209">
+        <v>101782.75</v>
       </c>
       <c r="E65" s="63">
-        <f t="shared" si="18"/>
-        <v>220000</v>
+        <f t="shared" si="22"/>
+        <v>101782.75</v>
       </c>
       <c r="F65" s="52"/>
       <c r="G65" s="36">
         <f t="shared" si="9"/>
-        <v>220000</v>
+        <v>101782.75</v>
       </c>
       <c r="H65" s="70">
         <f t="shared" si="10"/>
-        <v>220000</v>
+        <v>101782.75</v>
       </c>
       <c r="I65" s="79">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="J65" s="79">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="123" t="s">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="144" t="s">
+        <v>122</v>
+      </c>
+      <c r="B66" s="129"/>
+      <c r="C66" s="147"/>
+      <c r="D66" s="39">
+        <v>21900</v>
+      </c>
+      <c r="E66" s="63">
+        <f t="shared" si="22"/>
+        <v>21900</v>
+      </c>
+      <c r="F66" s="52"/>
+      <c r="G66" s="36">
+        <f t="shared" si="9"/>
+        <v>21900</v>
+      </c>
+      <c r="H66" s="70">
+        <f t="shared" si="10"/>
+        <v>21900</v>
+      </c>
+      <c r="I66" s="79">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J66" s="79">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="176" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="177"/>
+      <c r="C67" s="178"/>
+      <c r="D67" s="209">
+        <v>512600</v>
+      </c>
+      <c r="E67" s="63">
+        <f t="shared" si="22"/>
+        <v>512600</v>
+      </c>
+      <c r="F67" s="52"/>
+      <c r="G67" s="36">
+        <f t="shared" si="9"/>
+        <v>512600</v>
+      </c>
+      <c r="H67" s="70">
+        <f t="shared" si="10"/>
+        <v>512600</v>
+      </c>
+      <c r="I67" s="79">
+        <f t="shared" si="15"/>
+        <v>0</v>
+      </c>
+      <c r="J67" s="79">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A68" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="B66" s="127"/>
-      <c r="C66" s="127"/>
-      <c r="D66" s="35">
-        <f>SUM(D49:D65)</f>
-        <v>4871629.92</v>
-      </c>
-      <c r="E66" s="35">
-        <f>SUM(E49:E65)</f>
-        <v>4623694.2880029995</v>
-      </c>
-      <c r="F66" s="35">
-        <f>SUM(F49:F65)</f>
-        <v>247935.63199700002</v>
-      </c>
-      <c r="G66" s="36">
-        <f>E66+F66</f>
-        <v>4871629.92</v>
-      </c>
-      <c r="H66" s="64" t="str">
-        <f>IF(D66=G66, "", "Error")</f>
+      <c r="B68" s="127"/>
+      <c r="C68" s="127"/>
+      <c r="D68" s="35">
+        <f>SUM(D49:D67)</f>
+        <v>3263077.96</v>
+      </c>
+      <c r="E68" s="35">
+        <f>SUM(E49:E67)</f>
+        <v>3173095.2700780001</v>
+      </c>
+      <c r="F68" s="35">
+        <f>SUM(F49:F67)</f>
+        <v>89982.689922000005</v>
+      </c>
+      <c r="G68" s="36">
+        <f>E68+F68</f>
+        <v>3263077.96</v>
+      </c>
+      <c r="H68" s="64" t="str">
+        <f>IF(D68=G68, "", "Error")</f>
         <v/>
       </c>
-      <c r="I66" s="79">
-        <f>D66-G66</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="82"/>
-      <c r="B67" s="82"/>
-      <c r="C67" s="82"/>
-      <c r="D67" s="108"/>
-      <c r="E67" s="41"/>
-      <c r="F67" s="4"/>
-      <c r="H67" s="64"/>
-    </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="82"/>
-      <c r="B68" s="82"/>
-      <c r="C68" s="82"/>
-      <c r="D68" s="108"/>
-      <c r="E68" s="40"/>
-      <c r="F68" s="4"/>
-      <c r="H68" s="64"/>
-    </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="I68" s="79">
+        <f>D68-G68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="82"/>
       <c r="B69" s="82"/>
       <c r="C69" s="82"/>
       <c r="D69" s="108"/>
-      <c r="E69" s="40"/>
+      <c r="E69" s="41"/>
       <c r="F69" s="4"/>
       <c r="H69" s="64"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="125" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="105"/>
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="82"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="82"/>
-      <c r="D70" s="39">
+      <c r="D70" s="108"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="4"/>
+      <c r="H70" s="64"/>
+    </row>
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="82"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="82"/>
+      <c r="D71" s="108"/>
+      <c r="E71" s="40"/>
+      <c r="F71" s="4"/>
+      <c r="H71" s="64"/>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A72" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="B72" s="105"/>
+      <c r="C72" s="82"/>
+      <c r="D72" s="39">
         <v>82100</v>
       </c>
-      <c r="E70" s="63">
-        <f>D70*91.91%</f>
+      <c r="E72" s="63">
+        <f>D72*91.91%</f>
         <v>75458.109999999986</v>
       </c>
-      <c r="F70" s="52">
-        <f>D70*8.09%</f>
+      <c r="F72" s="52">
+        <f>D72*8.09%</f>
         <v>6641.89</v>
       </c>
-      <c r="G70" s="69"/>
-      <c r="H70" s="64"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="125" t="s">
-        <v>146</v>
-      </c>
-      <c r="B71" s="202"/>
-      <c r="C71" s="130"/>
-      <c r="D71" s="39">
-        <v>20900</v>
-      </c>
-      <c r="E71" s="63">
-        <f>D71*91.91%</f>
-        <v>19209.189999999999</v>
-      </c>
-      <c r="F71" s="52">
-        <f>D71*8.09%</f>
-        <v>1690.81</v>
-      </c>
-      <c r="G71" s="69"/>
-      <c r="H71" s="64"/>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A72" s="169" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="170"/>
-      <c r="C72" s="171"/>
-      <c r="D72" s="39">
-        <v>229300</v>
-      </c>
-      <c r="E72" s="63">
-        <f t="shared" ref="E72:E73" si="19">D72</f>
-        <v>229300</v>
-      </c>
-      <c r="F72" s="52"/>
       <c r="G72" s="69"/>
       <c r="H72" s="64"/>
     </row>
-    <row r="73" spans="1:10" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="169" t="s">
-        <v>119</v>
-      </c>
-      <c r="B73" s="170"/>
-      <c r="C73" s="171"/>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A73" s="125" t="s">
+        <v>129</v>
+      </c>
+      <c r="B73" s="148"/>
+      <c r="C73" s="130"/>
       <c r="D73" s="39">
+        <v>20900</v>
+      </c>
+      <c r="E73" s="63">
+        <f>D73*91.91%</f>
+        <v>19209.189999999999</v>
+      </c>
+      <c r="F73" s="52">
+        <f>D73*8.09%</f>
+        <v>1690.81</v>
+      </c>
+      <c r="G73" s="69"/>
+      <c r="H73" s="64"/>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A74" s="182" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="183"/>
+      <c r="C74" s="184"/>
+      <c r="D74" s="39">
+        <v>229300</v>
+      </c>
+      <c r="E74" s="63">
+        <f t="shared" ref="E74:E75" si="23">D74</f>
+        <v>229300</v>
+      </c>
+      <c r="F74" s="52"/>
+      <c r="G74" s="69"/>
+      <c r="H74" s="64"/>
+    </row>
+    <row r="75" spans="1:10" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="182" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="183"/>
+      <c r="C75" s="184"/>
+      <c r="D75" s="39">
         <v>227600</v>
       </c>
-      <c r="E73" s="63">
-        <f t="shared" si="19"/>
+      <c r="E75" s="63">
+        <f t="shared" si="23"/>
         <v>227600</v>
       </c>
-      <c r="F73" s="52"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="36"/>
-    </row>
-    <row r="74" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="123" t="s">
+      <c r="F75" s="52"/>
+      <c r="H75" s="64"/>
+      <c r="I75" s="36"/>
+    </row>
+    <row r="76" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="123" t="s">
         <v>16</v>
       </c>
-      <c r="B74" s="123"/>
-      <c r="C74" s="123"/>
-      <c r="D74" s="35">
-        <f>SUM(D70:D73)</f>
+      <c r="B76" s="123"/>
+      <c r="C76" s="123"/>
+      <c r="D76" s="35">
+        <f>SUM(D72:D75)</f>
         <v>559900</v>
       </c>
-      <c r="E74" s="35">
-        <f>SUM(E70:E73)</f>
+      <c r="E76" s="35">
+        <f>SUM(E72:E75)</f>
         <v>551567.30000000005</v>
       </c>
-      <c r="F74" s="35">
-        <f>SUM(F70:F73)</f>
+      <c r="F76" s="35">
+        <f>SUM(F72:F75)</f>
         <v>8332.7000000000007</v>
       </c>
-      <c r="G74" s="36">
-        <f>E74+F74</f>
+      <c r="G76" s="36">
+        <f>E76+F76</f>
         <v>559900</v>
       </c>
-      <c r="H74" s="64" t="str">
-        <f>IF(D74=G74, "", "Error")</f>
+      <c r="H76" s="64" t="str">
+        <f>IF(D76=G76, "", "Error")</f>
         <v/>
       </c>
-      <c r="J74" s="36"/>
-    </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="82"/>
-      <c r="B75" s="82"/>
-      <c r="C75" s="82"/>
-      <c r="D75" s="108"/>
-      <c r="E75" s="41"/>
-      <c r="F75" s="4"/>
-      <c r="H75" s="64"/>
-    </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="82"/>
-      <c r="B76" s="82"/>
-      <c r="C76" s="82"/>
-      <c r="D76" s="108"/>
-      <c r="E76" s="40"/>
-      <c r="F76" s="4"/>
-      <c r="H76" s="64"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="124" t="s">
-        <v>13</v>
-      </c>
+      <c r="J76" s="36"/>
+    </row>
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="82"/>
       <c r="B77" s="82"/>
       <c r="C77" s="82"/>
       <c r="D77" s="108"/>
-      <c r="E77" s="40"/>
+      <c r="E77" s="41"/>
       <c r="F77" s="4"/>
       <c r="H77" s="64"/>
     </row>
-    <row r="78" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="124" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="82" t="s">
-        <v>89</v>
-      </c>
-      <c r="C78" s="82" t="s">
-        <v>145</v>
-      </c>
-      <c r="D78" s="39"/>
-      <c r="E78" s="63">
-        <f>D78*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F78" s="52">
-        <f>D78*8.09%</f>
-        <v>0</v>
-      </c>
-      <c r="G78" t="s">
-        <v>116</v>
-      </c>
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="82"/>
+      <c r="B78" s="82"/>
+      <c r="C78" s="82"/>
+      <c r="D78" s="108"/>
+      <c r="E78" s="40"/>
+      <c r="F78" s="4"/>
       <c r="H78" s="64"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="124" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="B79" s="82"/>
       <c r="C79" s="82"/>
-      <c r="D79" s="39">
-        <v>45000</v>
-      </c>
-      <c r="E79" s="63">
-        <f>D79*91.91%</f>
-        <v>41359.499999999993</v>
-      </c>
-      <c r="F79" s="52">
-        <f>D79*8.09%</f>
-        <v>3640.5</v>
-      </c>
+      <c r="D79" s="108"/>
+      <c r="E79" s="40"/>
+      <c r="F79" s="4"/>
       <c r="H79" s="64"/>
-      <c r="J79" s="39"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="124" t="s">
-        <v>141</v>
-      </c>
-      <c r="B80" s="82"/>
-      <c r="C80" s="82"/>
-      <c r="D80" s="108">
-        <v>150000</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B80" s="82" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80" s="82" t="s">
+        <v>134</v>
+      </c>
+      <c r="D80" s="39"/>
       <c r="E80" s="63">
         <f>D80*91.91%</f>
-        <v>137865</v>
+        <v>0</v>
       </c>
       <c r="F80" s="52">
         <f>D80*8.09%</f>
-        <v>12135</v>
+        <v>0</v>
+      </c>
+      <c r="G80" t="s">
+        <v>113</v>
       </c>
       <c r="H80" s="64"/>
-      <c r="J80" s="36"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="123"/>
-      <c r="B81" s="123"/>
-      <c r="C81" s="123"/>
-      <c r="D81" s="35">
-        <f>SUM(D78:D80)</f>
-        <v>195000</v>
-      </c>
-      <c r="E81" s="35">
-        <f>SUM(E78:E80)</f>
-        <v>179224.5</v>
-      </c>
-      <c r="F81" s="35">
-        <f>SUM(F78:F80)</f>
-        <v>15775.5</v>
-      </c>
-      <c r="G81" s="36">
-        <f>E81+F81</f>
-        <v>195000</v>
-      </c>
-      <c r="H81" s="64" t="str">
-        <f>IF(D81=G81, "", "Error")</f>
-        <v/>
-      </c>
-      <c r="J81" s="36"/>
-    </row>
-    <row r="82" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="124" t="s">
-        <v>73</v>
-      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="124" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81" s="82"/>
+      <c r="C81" s="82"/>
+      <c r="D81" s="209">
+        <v>45000</v>
+      </c>
+      <c r="E81" s="63">
+        <f>D81*91.91%</f>
+        <v>41359.499999999993</v>
+      </c>
+      <c r="F81" s="52">
+        <f>D81*8.09%</f>
+        <v>3640.5</v>
+      </c>
+      <c r="H81" s="64"/>
+      <c r="J81" s="39"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="124"/>
       <c r="B82" s="82"/>
       <c r="C82" s="82"/>
-      <c r="D82" s="39"/>
-      <c r="E82" s="42"/>
-      <c r="F82" s="4"/>
+      <c r="D82" s="108"/>
+      <c r="E82" s="63">
+        <f>D82*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F82" s="52">
+        <f>D82*8.09%</f>
+        <v>0</v>
+      </c>
       <c r="H82" s="64"/>
-    </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="124" t="s">
+      <c r="J82" s="36"/>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A83" s="123"/>
+      <c r="B83" s="123"/>
+      <c r="C83" s="123"/>
+      <c r="D83" s="35">
+        <f>SUM(D80:D82)</f>
+        <v>45000</v>
+      </c>
+      <c r="E83" s="35">
+        <f>SUM(E80:E82)</f>
+        <v>41359.499999999993</v>
+      </c>
+      <c r="F83" s="35">
+        <f>SUM(F80:F82)</f>
+        <v>3640.5</v>
+      </c>
+      <c r="G83" s="36">
+        <f>E83+F83</f>
+        <v>44999.999999999993</v>
+      </c>
+      <c r="H83" s="64" t="str">
+        <f>IF(D83=G83, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="J83" s="36"/>
+    </row>
+    <row r="84" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="124" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="82"/>
+      <c r="C84" s="82"/>
+      <c r="D84" s="39"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="4"/>
+      <c r="H84" s="64"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A85" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="B83" s="82"/>
-      <c r="C83" s="82"/>
-      <c r="D83" s="39">
+      <c r="B85" s="82"/>
+      <c r="C85" s="82"/>
+      <c r="D85" s="39">
         <v>153381.85</v>
       </c>
-      <c r="E83" s="63">
-        <f>D83*91.91%</f>
+      <c r="E85" s="63">
+        <f>D85*91.91%</f>
         <v>140973.25833499999</v>
       </c>
-      <c r="F83" s="52">
-        <f>D83*8.09%</f>
+      <c r="F85" s="52">
+        <f>D85*8.09%</f>
         <v>12408.591665</v>
       </c>
-      <c r="H83" s="64"/>
-    </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A84" s="124" t="s">
+      <c r="H85" s="64"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A86" s="124" t="s">
         <v>75</v>
       </c>
-      <c r="B84" s="82"/>
-      <c r="C84" s="135"/>
-      <c r="D84" s="39">
+      <c r="B86" s="82"/>
+      <c r="C86" s="135"/>
+      <c r="D86" s="39">
         <v>57500</v>
       </c>
-      <c r="E84" s="63">
-        <f>D84*91.91%</f>
+      <c r="E86" s="63">
+        <f>D86*91.91%</f>
         <v>52848.249999999993</v>
       </c>
-      <c r="F84" s="52">
-        <f>D84*8.09%</f>
+      <c r="F86" s="52">
+        <f>D86*8.09%</f>
         <v>4651.75</v>
       </c>
-      <c r="H84" s="64"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="123" t="s">
+      <c r="H86" s="64"/>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A87" s="123" t="s">
         <v>15</v>
       </c>
-      <c r="B85" s="123"/>
-      <c r="C85" s="123"/>
-      <c r="D85" s="67">
-        <f>SUM(D83:D84)</f>
+      <c r="B87" s="123"/>
+      <c r="C87" s="123"/>
+      <c r="D87" s="67">
+        <f>SUM(D85:D86)</f>
         <v>210881.85</v>
       </c>
-      <c r="E85" s="61">
-        <f t="shared" ref="E85:F85" si="20">SUM(E83:E84)</f>
+      <c r="E87" s="61">
+        <f t="shared" ref="E87:F87" si="24">SUM(E85:E86)</f>
         <v>193821.50833499999</v>
       </c>
-      <c r="F85" s="61">
-        <f t="shared" si="20"/>
+      <c r="F87" s="61">
+        <f t="shared" si="24"/>
         <v>17060.341665</v>
-      </c>
-      <c r="G85" s="36">
-        <f>E85+F85</f>
-        <v>210881.84999999998</v>
-      </c>
-      <c r="H85" s="64" t="str">
-        <f>IF(D85=G85, "", "Error")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="82"/>
-      <c r="B86" s="82"/>
-      <c r="C86" s="82"/>
-      <c r="D86" s="82"/>
-      <c r="E86" s="8"/>
-      <c r="F86" s="4"/>
-      <c r="H86" s="64"/>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="136" t="s">
-        <v>105</v>
-      </c>
-      <c r="B87" s="136"/>
-      <c r="C87" s="136"/>
-      <c r="D87" s="83"/>
-      <c r="E87" s="43">
-        <f>D87*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F87" s="54">
-        <f>D87*8.09%</f>
-        <v>0</v>
       </c>
       <c r="G87" s="36">
         <f>E87+F87</f>
-        <v>0</v>
+        <v>210881.84999999998</v>
       </c>
       <c r="H87" s="64" t="str">
         <f>IF(D87=G87, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="137"/>
-      <c r="B88" s="81"/>
-      <c r="C88" s="81"/>
-      <c r="D88" s="81"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="66"/>
+    <row r="88" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="82"/>
+      <c r="B88" s="82"/>
+      <c r="C88" s="82"/>
+      <c r="D88" s="82"/>
+      <c r="E88" s="8"/>
+      <c r="F88" s="4"/>
       <c r="H88" s="64"/>
     </row>
-    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="138" t="s">
-        <v>76</v>
-      </c>
-      <c r="B89" s="139"/>
-      <c r="C89" s="140"/>
-      <c r="D89" s="84">
-        <f>SUM(D87+D85+D81+D74+D66+D47+D32+D27+D42)</f>
-        <v>8097597.3599999994</v>
-      </c>
-      <c r="E89" s="62">
-        <f>SUM(E87+E85+E81+E74+E66+E47+E32+E27+E42)</f>
-        <v>7635352.1721069999</v>
-      </c>
-      <c r="F89" s="62">
-        <f>SUM(F27+F42+F47+F66+F74+F81+F85+F87)</f>
-        <v>462245.18789300008</v>
+    <row r="89" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="136" t="s">
+        <v>103</v>
+      </c>
+      <c r="B89" s="136"/>
+      <c r="C89" s="136"/>
+      <c r="D89" s="83"/>
+      <c r="E89" s="43">
+        <f>D89*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="54">
+        <f>D89*8.09%</f>
+        <v>0</v>
       </c>
       <c r="G89" s="36">
         <f>E89+F89</f>
-        <v>8097597.3600000003</v>
+        <v>0</v>
       </c>
       <c r="H89" s="64" t="str">
         <f>IF(D89=G89, "", "Error")</f>
         <v/>
       </c>
-      <c r="I89" s="79">
-        <f>D89-G89</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="81"/>
+    </row>
+    <row r="90" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="137"/>
       <c r="B90" s="81"/>
       <c r="C90" s="81"/>
       <c r="D90" s="81"/>
-      <c r="E90" s="36"/>
-    </row>
-    <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="141" t="s">
-        <v>111</v>
-      </c>
-      <c r="B91" s="142"/>
-      <c r="C91" s="142"/>
-      <c r="D91" s="81"/>
-      <c r="E91" s="36"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="C92" s="57"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="6"/>
+      <c r="G90" s="66"/>
+      <c r="H90" s="64"/>
+    </row>
+    <row r="91" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="138" t="s">
+        <v>76</v>
+      </c>
+      <c r="B91" s="139"/>
+      <c r="C91" s="140"/>
+      <c r="D91" s="84">
+        <f>SUM(D89+D87+D83+D76+D68+D47+D32+D27+D42)</f>
+        <v>6333022.0600000005</v>
+      </c>
+      <c r="E91" s="62">
+        <f>SUM(E89+E87+E83+E76+E68+E47+E32+E27+E42)</f>
+        <v>6041352.1023880001</v>
+      </c>
+      <c r="F91" s="62">
+        <f>SUM(F27+F42+F47+F68+F76+F83+F87+F89)</f>
+        <v>291669.95761200006</v>
+      </c>
+      <c r="G91" s="36">
+        <f>E91+F91</f>
+        <v>6333022.0600000005</v>
+      </c>
+      <c r="H91" s="64" t="str">
+        <f>IF(D91=G91, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="I91" s="79">
+        <f>D91-G91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="81"/>
+      <c r="B92" s="81"/>
+      <c r="C92" s="81"/>
+      <c r="D92" s="81"/>
       <c r="E92" s="36"/>
     </row>
-    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="1"/>
-      <c r="C93" s="57"/>
+    <row r="93" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="141" t="s">
+        <v>109</v>
+      </c>
+      <c r="B93" s="142"/>
+      <c r="C93" s="142"/>
+      <c r="D93" s="81"/>
       <c r="E93" s="36"/>
     </row>
-    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="59" t="s">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="C94" s="57"/>
+      <c r="E94" s="36"/>
+    </row>
+    <row r="95" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="1"/>
+      <c r="C95" s="57"/>
+      <c r="E95" s="36"/>
+    </row>
+    <row r="96" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B94" s="60"/>
-      <c r="C94" s="58">
-        <f>SUM(C92:C93)</f>
-        <v>0</v>
-      </c>
-      <c r="E94" s="36"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E95" s="36"/>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="E96" s="55"/>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="164" t="s">
-        <v>86</v>
-      </c>
-      <c r="B97" s="165"/>
-      <c r="C97" s="165"/>
-      <c r="D97" s="165"/>
-      <c r="E97" s="76" t="s">
+      <c r="B96" s="60"/>
+      <c r="C96" s="58">
+        <f>SUM(C94:C95)</f>
+        <v>0</v>
+      </c>
+      <c r="E96" s="36"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E97" s="36"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="E98" s="55"/>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="171" t="s">
+        <v>85</v>
+      </c>
+      <c r="B99" s="172"/>
+      <c r="C99" s="172"/>
+      <c r="D99" s="172"/>
+      <c r="E99" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="F97" s="77" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="161"/>
-      <c r="B98" s="162"/>
-      <c r="C98" s="163"/>
-      <c r="D98" s="39"/>
-      <c r="E98" s="63">
-        <f t="shared" ref="E98:E99" si="21">D98*91.91%</f>
-        <v>0</v>
-      </c>
-      <c r="F98" s="52">
-        <f t="shared" ref="F98:F99" si="22">D98*8.09%</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="166"/>
-      <c r="B99" s="167"/>
-      <c r="C99" s="168"/>
-      <c r="D99" s="39"/>
-      <c r="E99" s="63">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="F99" s="52">
-        <f t="shared" si="22"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="158" t="s">
+      <c r="F99" s="77" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="168"/>
+      <c r="B100" s="169"/>
+      <c r="C100" s="170"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="63">
+        <f t="shared" ref="E100:E101" si="25">D100*91.91%</f>
+        <v>0</v>
+      </c>
+      <c r="F100" s="52">
+        <f t="shared" ref="F100:F101" si="26">D100*8.09%</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="173"/>
+      <c r="B101" s="174"/>
+      <c r="C101" s="175"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="63">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="F101" s="52">
+        <f t="shared" si="26"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="165" t="s">
         <v>25</v>
       </c>
-      <c r="B100" s="159"/>
-      <c r="C100" s="160"/>
-      <c r="D100" s="75">
-        <f>SUM(D98:D99)</f>
-        <v>0</v>
-      </c>
-      <c r="E100" s="75">
-        <f>SUM(E98:E99)</f>
-        <v>0</v>
-      </c>
-      <c r="F100" s="75">
-        <f>SUM(F98:F99)</f>
-        <v>0</v>
-      </c>
-      <c r="H100" s="36">
-        <f>E100+F100</f>
-        <v>0</v>
-      </c>
-      <c r="I100" s="64" t="str">
-        <f>IF(D100=H100, "", "Error")</f>
+      <c r="B102" s="166"/>
+      <c r="C102" s="167"/>
+      <c r="D102" s="75">
+        <f>SUM(D100:D101)</f>
+        <v>0</v>
+      </c>
+      <c r="E102" s="75">
+        <f>SUM(E100:E101)</f>
+        <v>0</v>
+      </c>
+      <c r="F102" s="75">
+        <f>SUM(F100:F101)</f>
+        <v>0</v>
+      </c>
+      <c r="H102" s="36">
+        <f>E102+F102</f>
+        <v>0</v>
+      </c>
+      <c r="I102" s="64" t="str">
+        <f>IF(D102=H102, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E102" s="36"/>
-    </row>
-    <row r="103" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="30" t="s">
+    <row r="104" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="E104" s="36"/>
+    </row>
+    <row r="105" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="B103" s="31">
-        <f>D89</f>
-        <v>8097597.3599999994</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="32" t="s">
+      <c r="B105" s="31">
+        <f>D91</f>
+        <v>6333022.0600000005</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="B104" s="33">
-        <f>D89-D87</f>
-        <v>8097597.3599999994</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D105" s="148"/>
-      <c r="E105" s="148"/>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="11" t="s">
+      <c r="B106" s="33">
+        <f>D91-D89</f>
+        <v>6333022.0600000005</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D107" s="155"/>
+      <c r="E107" s="155"/>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A108" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="B106" s="12"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="148"/>
-      <c r="E106" s="148"/>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+      <c r="B108" s="12"/>
+      <c r="C108" s="13"/>
+      <c r="D108" s="155"/>
+      <c r="E108" s="155"/>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A109" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B109" s="7">
         <v>5892489.5763089471</v>
       </c>
-      <c r="C107" s="15"/>
-      <c r="D107" s="148"/>
-      <c r="E107" s="148"/>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="16" t="s">
+      <c r="C109" s="15"/>
+      <c r="D109" s="155"/>
+      <c r="E109" s="155"/>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A110" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B108" s="25">
+      <c r="B110" s="25">
         <f>PRORRATEO!G52</f>
         <v>12695174.355166664</v>
       </c>
-      <c r="C108" s="15" t="s">
+      <c r="C110" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="D108" s="148"/>
-      <c r="E108" s="148"/>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B109" s="78">
-        <f>-B104</f>
-        <v>-8097597.3599999994</v>
-      </c>
-      <c r="C109" s="13"/>
-      <c r="D109" s="148"/>
-      <c r="E109" s="148"/>
-      <c r="G109" s="39"/>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="16" t="s">
+      <c r="D110" s="155"/>
+      <c r="E110" s="155"/>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A111" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="B110" s="78">
-        <f>-D100</f>
-        <v>0</v>
-      </c>
-      <c r="C110" s="13"/>
-      <c r="D110" s="148"/>
-      <c r="E110" s="148"/>
-      <c r="G110" s="46"/>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="16" t="s">
+      <c r="B111" s="78">
+        <f>-B106</f>
+        <v>-6333022.0600000005</v>
+      </c>
+      <c r="C111" s="13"/>
+      <c r="D111" s="155"/>
+      <c r="E111" s="155"/>
+      <c r="G111" s="39"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A112" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B112" s="78">
+        <f>-D102</f>
+        <v>0</v>
+      </c>
+      <c r="C112" s="13"/>
+      <c r="D112" s="155"/>
+      <c r="E112" s="155"/>
+      <c r="G112" s="46"/>
+    </row>
+    <row r="113" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A113" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B111" s="78">
-        <f>-B117</f>
+      <c r="B113" s="78">
+        <f>-B119</f>
         <v>-20000</v>
       </c>
-      <c r="C111" s="17"/>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B112" s="26">
-        <f>-C94</f>
-        <v>0</v>
-      </c>
-      <c r="C112" s="17"/>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A113" s="14" t="s">
+      <c r="C113" s="17"/>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A114" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B114" s="26">
+        <f>-C96</f>
+        <v>0</v>
+      </c>
+      <c r="C114" s="17"/>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A115" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B113" s="18">
-        <f>SUM(B107:B112)</f>
-        <v>10470066.57147561</v>
-      </c>
-      <c r="C113" s="65"/>
-      <c r="D113" s="36"/>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A114" s="17"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="20"/>
-    </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C115" s="13"/>
+      <c r="B115" s="18">
+        <f>SUM(B109:B114)</f>
+        <v>12234641.871475609</v>
+      </c>
+      <c r="C115" s="65"/>
       <c r="D115" s="36"/>
-      <c r="E115" s="79"/>
-    </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="11" t="s">
+    </row>
+    <row r="116" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A116" s="17"/>
+      <c r="C116" s="13"/>
+      <c r="D116" s="20"/>
+    </row>
+    <row r="117" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C117" s="13"/>
+      <c r="D117" s="36"/>
+      <c r="E117" s="79"/>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A118" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B116" s="90">
+      <c r="B118" s="90">
         <v>-122694.54000000004</v>
       </c>
-      <c r="C116" s="19"/>
-      <c r="D116" s="79"/>
-      <c r="E116" s="79"/>
-      <c r="F116" s="79"/>
-    </row>
-    <row r="117" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B117" s="26">
+      <c r="C118" s="19"/>
+      <c r="D118" s="79"/>
+      <c r="E118" s="79"/>
+      <c r="F118" s="79"/>
+    </row>
+    <row r="119" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B119" s="26">
         <v>20000</v>
       </c>
-      <c r="C117" s="19"/>
-      <c r="D117" s="79"/>
-      <c r="E117" s="85"/>
-    </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A118" s="14"/>
-      <c r="B118" s="78"/>
-      <c r="C118" s="19"/>
-      <c r="E118" s="36"/>
-    </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A119" s="14"/>
-      <c r="B119" s="78"/>
       <c r="C119" s="19"/>
-      <c r="D119" s="143"/>
-      <c r="E119" s="36"/>
-    </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A120" s="28" t="s">
+      <c r="D119" s="79"/>
+      <c r="E119" s="85"/>
+    </row>
+    <row r="120" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A120" s="14"/>
+      <c r="B120" s="78"/>
+      <c r="C120" s="19"/>
+      <c r="E120" s="36"/>
+    </row>
+    <row r="121" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A121" s="14"/>
+      <c r="B121" s="78"/>
+      <c r="C121" s="19"/>
+      <c r="D121" s="143"/>
+      <c r="E121" s="36"/>
+    </row>
+    <row r="122" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A122" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="B120" s="29">
-        <f>SUM(B116:B119)</f>
+      <c r="B122" s="29">
+        <f>SUM(B118:B121)</f>
         <v>-102694.54000000004</v>
       </c>
-      <c r="C120" s="19"/>
-    </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="C121" s="20"/>
-      <c r="D121" s="79"/>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B122" s="17"/>
-      <c r="C122" s="13"/>
-    </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="N124" s="8"/>
-    </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B127" s="147"/>
-      <c r="C127" s="147"/>
-      <c r="D127" s="147"/>
-      <c r="E127" s="147"/>
-    </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B128" s="147"/>
-      <c r="C128" s="147"/>
-      <c r="D128" s="147"/>
-      <c r="E128" s="147"/>
-    </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="147"/>
-      <c r="C129" s="147"/>
-      <c r="D129" s="147"/>
-      <c r="E129" s="147"/>
-    </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="147"/>
-      <c r="C130" s="147"/>
-      <c r="D130" s="147"/>
-      <c r="E130" s="147"/>
-    </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="147"/>
-      <c r="C131" s="147"/>
-      <c r="D131" s="147"/>
-      <c r="E131" s="147"/>
+      <c r="C122" s="19"/>
+    </row>
+    <row r="123" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C123" s="20"/>
+      <c r="D123" s="79"/>
+    </row>
+    <row r="124" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B124" s="17"/>
+      <c r="C124" s="13"/>
+    </row>
+    <row r="126" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N126" s="8"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B129" s="154"/>
+      <c r="C129" s="154"/>
+      <c r="D129" s="154"/>
+      <c r="E129" s="154"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B130" s="154"/>
+      <c r="C130" s="154"/>
+      <c r="D130" s="154"/>
+      <c r="E130" s="154"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B131" s="154"/>
+      <c r="C131" s="154"/>
+      <c r="D131" s="154"/>
+      <c r="E131" s="154"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B132" s="154"/>
+      <c r="C132" s="154"/>
+      <c r="D132" s="154"/>
+      <c r="E132" s="154"/>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B133" s="154"/>
+      <c r="C133" s="154"/>
+      <c r="D133" s="154"/>
+      <c r="E133" s="154"/>
     </row>
   </sheetData>
   <mergeCells count="12">
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B127:E131"/>
-    <mergeCell ref="D105:E110"/>
+    <mergeCell ref="B129:E133"/>
+    <mergeCell ref="D107:E112"/>
     <mergeCell ref="B14:D17"/>
+    <mergeCell ref="A102:C102"/>
     <mergeCell ref="A100:C100"/>
-    <mergeCell ref="A98:C98"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="A61:C61"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A101:C101"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A63:C63"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A74:C74"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3748,67 +3761,67 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R63"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" customWidth="1"/>
-    <col min="6" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" customWidth="1"/>
+    <col min="6" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" customWidth="1"/>
-    <col min="14" max="14" width="13.7109375" customWidth="1"/>
-    <col min="15" max="15" width="11.42578125" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.6640625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5546875" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="13.6640625" customWidth="1"/>
+    <col min="15" max="15" width="11.44140625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="184" t="str">
+    <row r="1" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="197" t="str">
         <f>RESUMEN!C5</f>
-        <v>VTO: 17/04</v>
-      </c>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="186"/>
+        <v>VTO: 15/05</v>
+      </c>
+      <c r="B1" s="198"/>
+      <c r="C1" s="198"/>
+      <c r="D1" s="198"/>
+      <c r="E1" s="198"/>
+      <c r="F1" s="198"/>
+      <c r="G1" s="198"/>
+      <c r="H1" s="198"/>
+      <c r="I1" s="198"/>
+      <c r="J1" s="199"/>
       <c r="K1" s="94" t="s">
-        <v>96</v>
-      </c>
-      <c r="L1" s="173">
-        <f>RESUMEN!D89</f>
-        <v>8097597.3599999994</v>
-      </c>
-      <c r="M1" s="174"/>
+        <v>95</v>
+      </c>
+      <c r="L1" s="188">
+        <f>RESUMEN!D91</f>
+        <v>6333022.0600000005</v>
+      </c>
+      <c r="M1" s="189"/>
       <c r="N1" s="95"/>
       <c r="O1" s="53">
         <f>L1*8.09%</f>
-        <v>655095.6264239999</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="187"/>
-      <c r="B2" s="188"/>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="188"/>
-      <c r="F2" s="188"/>
-      <c r="G2" s="188"/>
-      <c r="H2" s="188"/>
-      <c r="I2" s="188"/>
-      <c r="J2" s="189"/>
+        <v>512341.48465400003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="200"/>
+      <c r="B2" s="201"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="201"/>
+      <c r="E2" s="201"/>
+      <c r="F2" s="201"/>
+      <c r="G2" s="201"/>
+      <c r="H2" s="201"/>
+      <c r="I2" s="201"/>
+      <c r="J2" s="202"/>
       <c r="K2" s="96" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L2" s="5"/>
       <c r="M2" s="97">
@@ -3817,44 +3830,44 @@
       <c r="N2" s="98"/>
       <c r="O2" s="53">
         <f>O1-K7-553-50-86-8</f>
-        <v>192153.43853099982</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="187"/>
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
-      <c r="D3" s="188"/>
-      <c r="E3" s="188"/>
-      <c r="F3" s="188"/>
-      <c r="G3" s="188"/>
-      <c r="H3" s="188"/>
-      <c r="I3" s="188"/>
-      <c r="J3" s="189"/>
+        <v>49399.296760999947</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="200"/>
+      <c r="B3" s="201"/>
+      <c r="C3" s="201"/>
+      <c r="D3" s="201"/>
+      <c r="E3" s="201"/>
+      <c r="F3" s="201"/>
+      <c r="G3" s="201"/>
+      <c r="H3" s="201"/>
+      <c r="I3" s="201"/>
+      <c r="J3" s="202"/>
       <c r="K3" s="96" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L3" s="5"/>
       <c r="M3" s="99">
-        <f>RESUMEN!D100</f>
+        <f>RESUMEN!D102</f>
         <v>0</v>
       </c>
       <c r="N3" s="100"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="190"/>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
+    <row r="4" spans="1:16" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="203"/>
+      <c r="B4" s="204"/>
+      <c r="C4" s="204"/>
+      <c r="D4" s="204"/>
+      <c r="E4" s="204"/>
+      <c r="F4" s="204"/>
+      <c r="G4" s="204"/>
+      <c r="H4" s="204"/>
+      <c r="I4" s="204"/>
+      <c r="J4" s="205"/>
       <c r="K4" s="101" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L4" s="102"/>
       <c r="M4" s="103"/>
@@ -3864,67 +3877,67 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="177" t="s">
+    <row r="5" spans="1:16" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="185" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="193" t="s">
+      <c r="B5" s="206" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="177" t="s">
+      <c r="C5" s="185" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="182" t="s">
+      <c r="D5" s="195" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="177" t="s">
+      <c r="E5" s="185" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="177" t="s">
+      <c r="F5" s="185" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="177" t="s">
+      <c r="G5" s="185" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="179" t="s">
+      <c r="H5" s="192" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="182" t="s">
+      <c r="I5" s="195" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="175" t="s">
+      <c r="J5" s="190" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="175" t="s">
+      <c r="K5" s="190" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="175" t="s">
-        <v>120</v>
-      </c>
-      <c r="M5" s="175" t="s">
-        <v>122</v>
-      </c>
-      <c r="N5" s="175" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="178"/>
-      <c r="B6" s="194"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="195"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="183"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="176"/>
-      <c r="L6" s="181"/>
-      <c r="M6" s="176"/>
-      <c r="N6" s="176"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L5" s="190" t="s">
+        <v>117</v>
+      </c>
+      <c r="M5" s="190" t="s">
+        <v>119</v>
+      </c>
+      <c r="N5" s="190" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="186"/>
+      <c r="B6" s="207"/>
+      <c r="C6" s="186"/>
+      <c r="D6" s="208"/>
+      <c r="E6" s="186"/>
+      <c r="F6" s="186"/>
+      <c r="G6" s="186"/>
+      <c r="H6" s="193"/>
+      <c r="I6" s="196"/>
+      <c r="J6" s="194"/>
+      <c r="K6" s="191"/>
+      <c r="L6" s="194"/>
+      <c r="M6" s="191"/>
+      <c r="N6" s="191"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>26</v>
       </c>
@@ -3968,7 +3981,7 @@
         <v>489979.89916658006</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>28</v>
       </c>
@@ -4013,7 +4026,7 @@
         <v>199092.31304105348</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>28</v>
       </c>
@@ -4059,7 +4072,7 @@
         <v>379320.57903965254</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
@@ -4105,7 +4118,7 @@
         <v>255884</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>31</v>
       </c>
@@ -4152,7 +4165,7 @@
       </c>
       <c r="P11" s="36"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>34</v>
       </c>
@@ -4161,7 +4174,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E12" s="4">
         <v>2.84</v>
@@ -4198,7 +4211,7 @@
         <v>255884</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>34</v>
       </c>
@@ -4244,7 +4257,7 @@
         <v>309043.86646439624</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>36</v>
       </c>
@@ -4290,7 +4303,7 @@
         <v>523768.96666666662</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>36</v>
       </c>
@@ -4299,7 +4312,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E15" s="4">
         <v>3.43</v>
@@ -4336,7 +4349,7 @@
         <v>380028.08705170569</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>38</v>
       </c>
@@ -4345,7 +4358,7 @@
         <v>32</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E16" s="4">
         <v>2.84</v>
@@ -4382,7 +4395,7 @@
         <v>255884.08461662004</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>38</v>
       </c>
@@ -4428,7 +4441,7 @@
         <v>309043.32578511507</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>40</v>
       </c>
@@ -4437,7 +4450,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="51" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E18" s="4">
         <v>2.84</v>
@@ -4474,10 +4487,10 @@
         <v>255883.47402791301</v>
       </c>
       <c r="P18" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>40</v>
       </c>
@@ -4525,7 +4538,7 @@
         <v>330242.80882741156</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>43</v>
       </c>
@@ -4571,7 +4584,7 @@
         <v>255883.63520849921</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>43</v>
       </c>
@@ -4617,7 +4630,7 @@
         <v>309042.99501125532</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>46</v>
       </c>
@@ -4626,7 +4639,7 @@
         <v>38</v>
       </c>
       <c r="D22" s="72" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E22" s="4">
         <v>2.84</v>
@@ -4663,7 +4676,7 @@
         <v>255884</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
@@ -4711,7 +4724,7 @@
         <v>328280.58797762758</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>48</v>
       </c>
@@ -4757,7 +4770,7 @@
         <v>249932.49582633917</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
@@ -4766,7 +4779,7 @@
         <v>41</v>
       </c>
       <c r="D25" s="51" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E25" s="4">
         <v>3.43</v>
@@ -4805,7 +4818,7 @@
       <c r="Q25" s="56"/>
       <c r="R25" s="56"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>50</v>
       </c>
@@ -4830,7 +4843,7 @@
         <f t="shared" si="0"/>
         <v>-1598811.3406672962</v>
       </c>
-      <c r="I26" s="205">
+      <c r="I26" s="151">
         <v>46081</v>
       </c>
       <c r="J26" s="21">
@@ -4851,7 +4864,7 @@
         <v>-1154140.0211073339</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
@@ -4898,7 +4911,7 @@
       </c>
       <c r="R27" s="56"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>54</v>
       </c>
@@ -4944,7 +4957,7 @@
         <v>530626.64496279985</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>56</v>
       </c>
@@ -4990,7 +5003,7 @@
         <v>666147.19096574793</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30" s="47" t="s">
         <v>69</v>
       </c>
@@ -5034,7 +5047,7 @@
         <v>48654</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31" s="47" t="s">
         <v>69</v>
       </c>
@@ -5078,7 +5091,7 @@
         <v>49555</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32" s="47" t="s">
         <v>69</v>
       </c>
@@ -5122,7 +5135,7 @@
         <v>40545</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" s="47" t="s">
         <v>69</v>
       </c>
@@ -5140,7 +5153,7 @@
         <v>57746.666666666664</v>
       </c>
       <c r="G33" s="109">
-        <f t="shared" ref="G33:G34" si="5">F33</f>
+        <f t="shared" ref="G33" si="5">F33</f>
         <v>57746.666666666664</v>
       </c>
       <c r="H33" s="49">
@@ -5166,7 +5179,7 @@
         <v>54961</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="47" t="s">
         <v>69</v>
       </c>
@@ -5210,7 +5223,7 @@
         <v>48654</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="47" t="s">
         <v>69</v>
       </c>
@@ -5219,7 +5232,7 @@
         <v>6</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E35" s="4">
         <v>0.5</v>
@@ -5254,7 +5267,7 @@
         <v>45050</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="47" t="s">
         <v>69</v>
       </c>
@@ -5298,7 +5311,7 @@
         <v>45050</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="47" t="s">
         <v>69</v>
       </c>
@@ -5342,7 +5355,7 @@
         <v>44149</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="47" t="s">
         <v>69</v>
       </c>
@@ -5386,7 +5399,7 @@
         <v>44149</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="47" t="s">
         <v>69</v>
       </c>
@@ -5430,7 +5443,7 @@
         <v>53159</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="47" t="s">
         <v>69</v>
       </c>
@@ -5474,7 +5487,7 @@
         <v>51357</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="47" t="s">
         <v>69</v>
       </c>
@@ -5518,7 +5531,7 @@
         <v>48654</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="47" t="s">
         <v>69</v>
       </c>
@@ -5562,7 +5575,7 @@
         <v>49555</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" s="47" t="s">
         <v>69</v>
       </c>
@@ -5607,10 +5620,10 @@
       </c>
       <c r="P43" s="36">
         <f>L1-K52</f>
-        <v>-176997.8278930001</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+        <v>-1941573.127892999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" s="47" t="s">
         <v>69</v>
       </c>
@@ -5654,7 +5667,7 @@
         <v>54961</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" s="47" t="s">
         <v>69</v>
       </c>
@@ -5698,7 +5711,7 @@
         <v>48654</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" s="47" t="s">
         <v>69</v>
       </c>
@@ -5742,10 +5755,10 @@
         <v>45050</v>
       </c>
       <c r="Q46" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" s="47" t="s">
         <v>69</v>
       </c>
@@ -5794,7 +5807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" s="47" t="s">
         <v>69</v>
       </c>
@@ -5838,7 +5851,7 @@
         <v>44149</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="47" t="s">
         <v>69</v>
       </c>
@@ -5883,7 +5896,7 @@
         <v>44149</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="47" t="s">
         <v>69</v>
       </c>
@@ -5927,7 +5940,7 @@
         <v>53159</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="47" t="s">
         <v>69</v>
       </c>
@@ -5971,7 +5984,7 @@
         <v>51357</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -6012,41 +6025,41 @@
       </c>
       <c r="P52" s="53"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="K53" s="56">
         <f>K52-L1</f>
-        <v>176997.8278930001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="172"/>
-      <c r="D54" s="172"/>
-      <c r="E54" s="172"/>
-      <c r="F54" s="172"/>
-      <c r="G54" s="172"/>
-      <c r="H54" s="172"/>
-      <c r="I54" s="172"/>
-      <c r="J54" s="172"/>
-      <c r="K54" s="172"/>
-      <c r="L54" s="172"/>
-      <c r="M54" s="172"/>
-      <c r="N54" s="172"/>
-    </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="172"/>
-      <c r="D55" s="172"/>
-      <c r="E55" s="172"/>
-      <c r="F55" s="172"/>
-      <c r="G55" s="172"/>
-      <c r="H55" s="172"/>
-      <c r="I55" s="172"/>
-      <c r="J55" s="172"/>
-      <c r="K55" s="172"/>
-      <c r="L55" s="172"/>
-      <c r="M55" s="172"/>
-      <c r="N55" s="172"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+        <v>1941573.127892999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="187"/>
+      <c r="D54" s="187"/>
+      <c r="E54" s="187"/>
+      <c r="F54" s="187"/>
+      <c r="G54" s="187"/>
+      <c r="H54" s="187"/>
+      <c r="I54" s="187"/>
+      <c r="J54" s="187"/>
+      <c r="K54" s="187"/>
+      <c r="L54" s="187"/>
+      <c r="M54" s="187"/>
+      <c r="N54" s="187"/>
+    </row>
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="187"/>
+      <c r="D55" s="187"/>
+      <c r="E55" s="187"/>
+      <c r="F55" s="187"/>
+      <c r="G55" s="187"/>
+      <c r="H55" s="187"/>
+      <c r="I55" s="187"/>
+      <c r="J55" s="187"/>
+      <c r="K55" s="187"/>
+      <c r="L55" s="187"/>
+      <c r="M55" s="187"/>
+      <c r="N55" s="187"/>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="C56" s="73"/>
       <c r="D56" s="73"/>
       <c r="E56" s="73"/>
@@ -6060,108 +6073,110 @@
       <c r="M56" s="73"/>
       <c r="N56" s="73"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="172" t="s">
-        <v>101</v>
-      </c>
-      <c r="D57" s="172"/>
-      <c r="E57" s="172"/>
-      <c r="F57" s="172"/>
-      <c r="G57" s="172"/>
-      <c r="H57" s="172"/>
-      <c r="I57" s="172"/>
-      <c r="J57" s="172"/>
-      <c r="K57" s="172"/>
-      <c r="L57" s="172"/>
-      <c r="M57" s="172"/>
-      <c r="N57" s="172"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="172"/>
-      <c r="D58" s="172"/>
-      <c r="E58" s="172"/>
-      <c r="F58" s="172"/>
-      <c r="G58" s="172"/>
-      <c r="H58" s="172"/>
-      <c r="I58" s="172"/>
-      <c r="J58" s="172"/>
-      <c r="K58" s="172"/>
-      <c r="L58" s="172"/>
-      <c r="M58" s="172"/>
-      <c r="N58" s="172"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="172"/>
-      <c r="D59" s="172"/>
-      <c r="E59" s="172"/>
-      <c r="F59" s="172"/>
-      <c r="G59" s="172"/>
-      <c r="H59" s="172"/>
-      <c r="I59" s="172"/>
-      <c r="J59" s="172"/>
-      <c r="K59" s="172"/>
-      <c r="L59" s="172"/>
-      <c r="M59" s="172"/>
-      <c r="N59" s="172"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="172"/>
-      <c r="D60" s="172"/>
-      <c r="E60" s="172"/>
-      <c r="F60" s="172"/>
-      <c r="G60" s="172"/>
-      <c r="H60" s="172"/>
-      <c r="I60" s="172"/>
-      <c r="J60" s="172"/>
-      <c r="K60" s="172"/>
-      <c r="L60" s="172"/>
-      <c r="M60" s="172"/>
-      <c r="N60" s="172"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="172"/>
-      <c r="D61" s="172"/>
-      <c r="E61" s="172"/>
-      <c r="F61" s="172"/>
-      <c r="G61" s="172"/>
-      <c r="H61" s="172"/>
-      <c r="I61" s="172"/>
-      <c r="J61" s="172"/>
-      <c r="K61" s="172"/>
-      <c r="L61" s="172"/>
-      <c r="M61" s="172"/>
-      <c r="N61" s="172"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="172"/>
-      <c r="D62" s="172"/>
-      <c r="E62" s="172"/>
-      <c r="F62" s="172"/>
-      <c r="G62" s="172"/>
-      <c r="H62" s="172"/>
-      <c r="I62" s="172"/>
-      <c r="J62" s="172"/>
-      <c r="K62" s="172"/>
-      <c r="L62" s="172"/>
-      <c r="M62" s="172"/>
-      <c r="N62" s="172"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="172"/>
-      <c r="D63" s="172"/>
-      <c r="E63" s="172"/>
-      <c r="F63" s="172"/>
-      <c r="G63" s="172"/>
-      <c r="H63" s="172"/>
-      <c r="I63" s="172"/>
-      <c r="J63" s="172"/>
-      <c r="K63" s="172"/>
-      <c r="L63" s="172"/>
-      <c r="M63" s="172"/>
-      <c r="N63" s="172"/>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C57" s="187" t="s">
+        <v>100</v>
+      </c>
+      <c r="D57" s="187"/>
+      <c r="E57" s="187"/>
+      <c r="F57" s="187"/>
+      <c r="G57" s="187"/>
+      <c r="H57" s="187"/>
+      <c r="I57" s="187"/>
+      <c r="J57" s="187"/>
+      <c r="K57" s="187"/>
+      <c r="L57" s="187"/>
+      <c r="M57" s="187"/>
+      <c r="N57" s="187"/>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C58" s="187"/>
+      <c r="D58" s="187"/>
+      <c r="E58" s="187"/>
+      <c r="F58" s="187"/>
+      <c r="G58" s="187"/>
+      <c r="H58" s="187"/>
+      <c r="I58" s="187"/>
+      <c r="J58" s="187"/>
+      <c r="K58" s="187"/>
+      <c r="L58" s="187"/>
+      <c r="M58" s="187"/>
+      <c r="N58" s="187"/>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C59" s="187"/>
+      <c r="D59" s="187"/>
+      <c r="E59" s="187"/>
+      <c r="F59" s="187"/>
+      <c r="G59" s="187"/>
+      <c r="H59" s="187"/>
+      <c r="I59" s="187"/>
+      <c r="J59" s="187"/>
+      <c r="K59" s="187"/>
+      <c r="L59" s="187"/>
+      <c r="M59" s="187"/>
+      <c r="N59" s="187"/>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C60" s="187"/>
+      <c r="D60" s="187"/>
+      <c r="E60" s="187"/>
+      <c r="F60" s="187"/>
+      <c r="G60" s="187"/>
+      <c r="H60" s="187"/>
+      <c r="I60" s="187"/>
+      <c r="J60" s="187"/>
+      <c r="K60" s="187"/>
+      <c r="L60" s="187"/>
+      <c r="M60" s="187"/>
+      <c r="N60" s="187"/>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C61" s="187"/>
+      <c r="D61" s="187"/>
+      <c r="E61" s="187"/>
+      <c r="F61" s="187"/>
+      <c r="G61" s="187"/>
+      <c r="H61" s="187"/>
+      <c r="I61" s="187"/>
+      <c r="J61" s="187"/>
+      <c r="K61" s="187"/>
+      <c r="L61" s="187"/>
+      <c r="M61" s="187"/>
+      <c r="N61" s="187"/>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C62" s="187"/>
+      <c r="D62" s="187"/>
+      <c r="E62" s="187"/>
+      <c r="F62" s="187"/>
+      <c r="G62" s="187"/>
+      <c r="H62" s="187"/>
+      <c r="I62" s="187"/>
+      <c r="J62" s="187"/>
+      <c r="K62" s="187"/>
+      <c r="L62" s="187"/>
+      <c r="M62" s="187"/>
+      <c r="N62" s="187"/>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C63" s="187"/>
+      <c r="D63" s="187"/>
+      <c r="E63" s="187"/>
+      <c r="F63" s="187"/>
+      <c r="G63" s="187"/>
+      <c r="H63" s="187"/>
+      <c r="I63" s="187"/>
+      <c r="J63" s="187"/>
+      <c r="K63" s="187"/>
+      <c r="L63" s="187"/>
+      <c r="M63" s="187"/>
+      <c r="N63" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
@@ -6178,8 +6193,6 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
@@ -6189,11 +6202,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2666E70F-CDC7-456F-AF96-2906778A9145}">
   <dimension ref="C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82C2FB3-30D3-424D-812D-80D6EB102191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4985B0C-F206-4B9F-8049-4552540BB5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -523,7 +523,7 @@
     <numFmt numFmtId="166" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -685,13 +685,6 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1095,7 +1088,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1295,7 +1288,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="6" fontId="23" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="2" fillId="3" borderId="21" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1383,6 +1375,9 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1451,9 +1446,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1873,13 +1865,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="90"/>
-      <c r="B1" s="155" t="s">
+      <c r="B1" s="154" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="155"/>
-      <c r="D1" s="155"/>
-      <c r="E1" s="155"/>
-      <c r="F1" s="156"/>
+      <c r="C1" s="154"/>
+      <c r="D1" s="154"/>
+      <c r="E1" s="154"/>
+      <c r="F1" s="155"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="7"/>
@@ -1983,29 +1975,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="78"/>
-      <c r="B14" s="159" t="s">
+      <c r="B14" s="158" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="160"/>
-      <c r="D14" s="161"/>
+      <c r="C14" s="159"/>
+      <c r="D14" s="160"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="78"/>
-      <c r="B15" s="162"/>
-      <c r="C15" s="163"/>
-      <c r="D15" s="164"/>
+      <c r="B15" s="161"/>
+      <c r="C15" s="162"/>
+      <c r="D15" s="163"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="78"/>
-      <c r="B16" s="162"/>
-      <c r="C16" s="163"/>
-      <c r="D16" s="164"/>
+      <c r="B16" s="161"/>
+      <c r="C16" s="162"/>
+      <c r="D16" s="163"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="78"/>
-      <c r="B17" s="165"/>
-      <c r="C17" s="166"/>
-      <c r="D17" s="167"/>
+      <c r="B17" s="164"/>
+      <c r="C17" s="165"/>
+      <c r="D17" s="166"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="78"/>
@@ -2047,7 +2039,7 @@
         <v>122</v>
       </c>
       <c r="C22" s="79"/>
-      <c r="D22" s="154"/>
+      <c r="D22" s="153"/>
       <c r="E22" s="82"/>
       <c r="F22" s="82"/>
     </row>
@@ -2827,11 +2819,11 @@
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="182" t="s">
+      <c r="A60" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="B60" s="183"/>
-      <c r="C60" s="184"/>
+      <c r="B60" s="182"/>
+      <c r="C60" s="183"/>
       <c r="D60" s="37">
         <v>580000</v>
       </c>
@@ -2883,11 +2875,11 @@
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="182" t="s">
+      <c r="A62" s="181" t="s">
         <v>129</v>
       </c>
-      <c r="B62" s="183"/>
-      <c r="C62" s="184"/>
+      <c r="B62" s="182"/>
+      <c r="C62" s="183"/>
       <c r="D62" s="37">
         <v>19800</v>
       </c>
@@ -3007,9 +2999,9 @@
       </c>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="179"/>
-      <c r="B66" s="180"/>
-      <c r="C66" s="181"/>
+      <c r="A66" s="178"/>
+      <c r="B66" s="179"/>
+      <c r="C66" s="180"/>
       <c r="D66" s="37"/>
       <c r="E66" s="60">
         <f t="shared" si="20"/>
@@ -3480,12 +3472,12 @@
       <c r="E96" s="52"/>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="174" t="s">
+      <c r="A97" s="173" t="s">
         <v>85</v>
       </c>
-      <c r="B97" s="175"/>
-      <c r="C97" s="175"/>
-      <c r="D97" s="175"/>
+      <c r="B97" s="174"/>
+      <c r="C97" s="174"/>
+      <c r="D97" s="174"/>
       <c r="E97" s="73" t="s">
         <v>19</v>
       </c>
@@ -3494,11 +3486,11 @@
       </c>
     </row>
     <row r="98" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A98" s="171" t="s">
+      <c r="A98" s="170" t="s">
         <v>133</v>
       </c>
-      <c r="B98" s="172"/>
-      <c r="C98" s="173"/>
+      <c r="B98" s="171"/>
+      <c r="C98" s="172"/>
       <c r="D98" s="37">
         <v>512600</v>
       </c>
@@ -3512,11 +3504,11 @@
       </c>
     </row>
     <row r="99" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="176" t="s">
+      <c r="A99" s="175" t="s">
         <v>142</v>
       </c>
-      <c r="B99" s="177"/>
-      <c r="C99" s="178"/>
+      <c r="B99" s="176"/>
+      <c r="C99" s="177"/>
       <c r="D99" s="37">
         <v>300000</v>
       </c>
@@ -3530,11 +3522,11 @@
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="168" t="s">
+      <c r="A100" s="167" t="s">
         <v>25</v>
       </c>
-      <c r="B100" s="169"/>
-      <c r="C100" s="170"/>
+      <c r="B100" s="168"/>
+      <c r="C100" s="169"/>
       <c r="D100" s="72">
         <f>SUM(D98:D99)</f>
         <v>812600</v>
@@ -3578,8 +3570,8 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="D105" s="158"/>
-      <c r="E105" s="158"/>
+      <c r="D105" s="157"/>
+      <c r="E105" s="157"/>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
@@ -3587,8 +3579,8 @@
       </c>
       <c r="B106" s="10"/>
       <c r="C106" s="11"/>
-      <c r="D106" s="158"/>
-      <c r="E106" s="158"/>
+      <c r="D106" s="157"/>
+      <c r="E106" s="157"/>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="12" t="s">
@@ -3598,8 +3590,8 @@
         <v>10470066.57147561</v>
       </c>
       <c r="C107" s="13"/>
-      <c r="D107" s="158"/>
-      <c r="E107" s="158"/>
+      <c r="D107" s="157"/>
+      <c r="E107" s="157"/>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="14" t="s">
@@ -3612,8 +3604,8 @@
       <c r="C108" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="D108" s="158"/>
-      <c r="E108" s="158"/>
+      <c r="D108" s="157"/>
+      <c r="E108" s="157"/>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="14" t="s">
@@ -3624,8 +3616,8 @@
         <v>-5542413.25</v>
       </c>
       <c r="C109" s="11"/>
-      <c r="D109" s="158"/>
-      <c r="E109" s="158"/>
+      <c r="D109" s="157"/>
+      <c r="E109" s="157"/>
       <c r="G109" s="37"/>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -3637,8 +3629,8 @@
         <v>-812600</v>
       </c>
       <c r="C110" s="11"/>
-      <c r="D110" s="158"/>
-      <c r="E110" s="158"/>
+      <c r="D110" s="157"/>
+      <c r="E110" s="157"/>
       <c r="G110" s="43"/>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -3745,34 +3737,34 @@
       <c r="N124" s="6"/>
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B127" s="157"/>
-      <c r="C127" s="157"/>
-      <c r="D127" s="157"/>
-      <c r="E127" s="157"/>
+      <c r="B127" s="156"/>
+      <c r="C127" s="156"/>
+      <c r="D127" s="156"/>
+      <c r="E127" s="156"/>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B128" s="157"/>
-      <c r="C128" s="157"/>
-      <c r="D128" s="157"/>
-      <c r="E128" s="157"/>
+      <c r="B128" s="156"/>
+      <c r="C128" s="156"/>
+      <c r="D128" s="156"/>
+      <c r="E128" s="156"/>
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="157"/>
-      <c r="C129" s="157"/>
-      <c r="D129" s="157"/>
-      <c r="E129" s="157"/>
+      <c r="B129" s="156"/>
+      <c r="C129" s="156"/>
+      <c r="D129" s="156"/>
+      <c r="E129" s="156"/>
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="157"/>
-      <c r="C130" s="157"/>
-      <c r="D130" s="157"/>
-      <c r="E130" s="157"/>
+      <c r="B130" s="156"/>
+      <c r="C130" s="156"/>
+      <c r="D130" s="156"/>
+      <c r="E130" s="156"/>
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B131" s="157"/>
-      <c r="C131" s="157"/>
-      <c r="D131" s="157"/>
-      <c r="E131" s="157"/>
+      <c r="B131" s="156"/>
+      <c r="C131" s="156"/>
+      <c r="D131" s="156"/>
+      <c r="E131" s="156"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -4468,14 +4460,16 @@
         <f t="shared" si="3"/>
         <v>263677.82</v>
       </c>
-      <c r="L17" s="88"/>
+      <c r="L17" s="88">
+        <v>20000</v>
+      </c>
       <c r="M17" s="2">
         <f t="shared" si="4"/>
-        <v>286501.30734444817</v>
+        <v>306501.30734444817</v>
       </c>
       <c r="N17" s="5">
         <f t="shared" si="1"/>
-        <v>303691.38578511507</v>
+        <v>324891.38578511507</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
@@ -4514,7 +4508,7 @@
         <f t="shared" si="3"/>
         <v>218322.16</v>
       </c>
-      <c r="L18" s="153">
+      <c r="L18" s="88">
         <v>20000</v>
       </c>
       <c r="M18" s="2">
@@ -6038,15 +6032,15 @@
       </c>
       <c r="L52" s="87">
         <f>SUM(L7:L51)</f>
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="M52" s="22">
         <f>SUM(M7:M51)</f>
-        <v>6479211.0980660357</v>
+        <v>6499211.0980660357</v>
       </c>
       <c r="N52" s="21">
         <f>SUM(N7:N51)</f>
-        <v>6867963.7639499977</v>
+        <v>6889163.7639499977</v>
       </c>
       <c r="P52" s="50"/>
     </row>
@@ -6057,32 +6051,32 @@
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="208"/>
-      <c r="D54" s="208"/>
-      <c r="E54" s="208"/>
-      <c r="F54" s="208"/>
-      <c r="G54" s="208"/>
-      <c r="H54" s="208"/>
-      <c r="I54" s="208"/>
-      <c r="J54" s="208"/>
-      <c r="K54" s="208"/>
-      <c r="L54" s="208"/>
-      <c r="M54" s="208"/>
-      <c r="N54" s="208"/>
+      <c r="C54" s="184"/>
+      <c r="D54" s="184"/>
+      <c r="E54" s="184"/>
+      <c r="F54" s="184"/>
+      <c r="G54" s="184"/>
+      <c r="H54" s="184"/>
+      <c r="I54" s="184"/>
+      <c r="J54" s="184"/>
+      <c r="K54" s="184"/>
+      <c r="L54" s="184"/>
+      <c r="M54" s="184"/>
+      <c r="N54" s="184"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="208"/>
-      <c r="D55" s="208"/>
-      <c r="E55" s="208"/>
-      <c r="F55" s="208"/>
-      <c r="G55" s="208"/>
-      <c r="H55" s="208"/>
-      <c r="I55" s="208"/>
-      <c r="J55" s="208"/>
-      <c r="K55" s="208"/>
-      <c r="L55" s="208"/>
-      <c r="M55" s="208"/>
-      <c r="N55" s="208"/>
+      <c r="C55" s="184"/>
+      <c r="D55" s="184"/>
+      <c r="E55" s="184"/>
+      <c r="F55" s="184"/>
+      <c r="G55" s="184"/>
+      <c r="H55" s="184"/>
+      <c r="I55" s="184"/>
+      <c r="J55" s="184"/>
+      <c r="K55" s="184"/>
+      <c r="L55" s="184"/>
+      <c r="M55" s="184"/>
+      <c r="N55" s="184"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6099,107 +6093,109 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="208" t="s">
+      <c r="C57" s="184" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="208"/>
-      <c r="E57" s="208"/>
-      <c r="F57" s="208"/>
-      <c r="G57" s="208"/>
-      <c r="H57" s="208"/>
-      <c r="I57" s="208"/>
-      <c r="J57" s="208"/>
-      <c r="K57" s="208"/>
-      <c r="L57" s="208"/>
-      <c r="M57" s="208"/>
-      <c r="N57" s="208"/>
+      <c r="D57" s="184"/>
+      <c r="E57" s="184"/>
+      <c r="F57" s="184"/>
+      <c r="G57" s="184"/>
+      <c r="H57" s="184"/>
+      <c r="I57" s="184"/>
+      <c r="J57" s="184"/>
+      <c r="K57" s="184"/>
+      <c r="L57" s="184"/>
+      <c r="M57" s="184"/>
+      <c r="N57" s="184"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="208"/>
-      <c r="D58" s="208"/>
-      <c r="E58" s="208"/>
-      <c r="F58" s="208"/>
-      <c r="G58" s="208"/>
-      <c r="H58" s="208"/>
-      <c r="I58" s="208"/>
-      <c r="J58" s="208"/>
-      <c r="K58" s="208"/>
-      <c r="L58" s="208"/>
-      <c r="M58" s="208"/>
-      <c r="N58" s="208"/>
+      <c r="C58" s="184"/>
+      <c r="D58" s="184"/>
+      <c r="E58" s="184"/>
+      <c r="F58" s="184"/>
+      <c r="G58" s="184"/>
+      <c r="H58" s="184"/>
+      <c r="I58" s="184"/>
+      <c r="J58" s="184"/>
+      <c r="K58" s="184"/>
+      <c r="L58" s="184"/>
+      <c r="M58" s="184"/>
+      <c r="N58" s="184"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="208"/>
-      <c r="D59" s="208"/>
-      <c r="E59" s="208"/>
-      <c r="F59" s="208"/>
-      <c r="G59" s="208"/>
-      <c r="H59" s="208"/>
-      <c r="I59" s="208"/>
-      <c r="J59" s="208"/>
-      <c r="K59" s="208"/>
-      <c r="L59" s="208"/>
-      <c r="M59" s="208"/>
-      <c r="N59" s="208"/>
+      <c r="C59" s="184"/>
+      <c r="D59" s="184"/>
+      <c r="E59" s="184"/>
+      <c r="F59" s="184"/>
+      <c r="G59" s="184"/>
+      <c r="H59" s="184"/>
+      <c r="I59" s="184"/>
+      <c r="J59" s="184"/>
+      <c r="K59" s="184"/>
+      <c r="L59" s="184"/>
+      <c r="M59" s="184"/>
+      <c r="N59" s="184"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="208"/>
-      <c r="D60" s="208"/>
-      <c r="E60" s="208"/>
-      <c r="F60" s="208"/>
-      <c r="G60" s="208"/>
-      <c r="H60" s="208"/>
-      <c r="I60" s="208"/>
-      <c r="J60" s="208"/>
-      <c r="K60" s="208"/>
-      <c r="L60" s="208"/>
-      <c r="M60" s="208"/>
-      <c r="N60" s="208"/>
+      <c r="C60" s="184"/>
+      <c r="D60" s="184"/>
+      <c r="E60" s="184"/>
+      <c r="F60" s="184"/>
+      <c r="G60" s="184"/>
+      <c r="H60" s="184"/>
+      <c r="I60" s="184"/>
+      <c r="J60" s="184"/>
+      <c r="K60" s="184"/>
+      <c r="L60" s="184"/>
+      <c r="M60" s="184"/>
+      <c r="N60" s="184"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="208"/>
-      <c r="D61" s="208"/>
-      <c r="E61" s="208"/>
-      <c r="F61" s="208"/>
-      <c r="G61" s="208"/>
-      <c r="H61" s="208"/>
-      <c r="I61" s="208"/>
-      <c r="J61" s="208"/>
-      <c r="K61" s="208"/>
-      <c r="L61" s="208"/>
-      <c r="M61" s="208"/>
-      <c r="N61" s="208"/>
+      <c r="C61" s="184"/>
+      <c r="D61" s="184"/>
+      <c r="E61" s="184"/>
+      <c r="F61" s="184"/>
+      <c r="G61" s="184"/>
+      <c r="H61" s="184"/>
+      <c r="I61" s="184"/>
+      <c r="J61" s="184"/>
+      <c r="K61" s="184"/>
+      <c r="L61" s="184"/>
+      <c r="M61" s="184"/>
+      <c r="N61" s="184"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="208"/>
-      <c r="D62" s="208"/>
-      <c r="E62" s="208"/>
-      <c r="F62" s="208"/>
-      <c r="G62" s="208"/>
-      <c r="H62" s="208"/>
-      <c r="I62" s="208"/>
-      <c r="J62" s="208"/>
-      <c r="K62" s="208"/>
-      <c r="L62" s="208"/>
-      <c r="M62" s="208"/>
-      <c r="N62" s="208"/>
+      <c r="C62" s="184"/>
+      <c r="D62" s="184"/>
+      <c r="E62" s="184"/>
+      <c r="F62" s="184"/>
+      <c r="G62" s="184"/>
+      <c r="H62" s="184"/>
+      <c r="I62" s="184"/>
+      <c r="J62" s="184"/>
+      <c r="K62" s="184"/>
+      <c r="L62" s="184"/>
+      <c r="M62" s="184"/>
+      <c r="N62" s="184"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="208"/>
-      <c r="D63" s="208"/>
-      <c r="E63" s="208"/>
-      <c r="F63" s="208"/>
-      <c r="G63" s="208"/>
-      <c r="H63" s="208"/>
-      <c r="I63" s="208"/>
-      <c r="J63" s="208"/>
-      <c r="K63" s="208"/>
-      <c r="L63" s="208"/>
-      <c r="M63" s="208"/>
-      <c r="N63" s="208"/>
+      <c r="C63" s="184"/>
+      <c r="D63" s="184"/>
+      <c r="E63" s="184"/>
+      <c r="F63" s="184"/>
+      <c r="G63" s="184"/>
+      <c r="H63" s="184"/>
+      <c r="I63" s="184"/>
+      <c r="J63" s="184"/>
+      <c r="K63" s="184"/>
+      <c r="L63" s="184"/>
+      <c r="M63" s="184"/>
+      <c r="N63" s="184"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
     <mergeCell ref="C54:N55"/>
     <mergeCell ref="L1:M1"/>
@@ -6216,8 +6212,6 @@
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="F5:F6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>

--- a/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
+++ b/2026/BELGRANO 1646/Abril/Abril-BLG1646.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BELGRANO 1646\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4985B0C-F206-4B9F-8049-4552540BB5C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA97ED2-7E99-4934-A5B7-0E12C8E59D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -1375,6 +1375,12 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1389,12 +1395,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3826,11 +3826,11 @@
       <c r="K1" s="90" t="s">
         <v>94</v>
       </c>
-      <c r="L1" s="185">
+      <c r="L1" s="187">
         <f>RESUMEN!D89</f>
         <v>5542413.25</v>
       </c>
-      <c r="M1" s="186"/>
+      <c r="M1" s="188"/>
       <c r="N1" s="91"/>
       <c r="O1" s="50">
         <f>L1*8.09%</f>
@@ -3909,25 +3909,25 @@
       </c>
     </row>
     <row r="5" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="189" t="s">
+      <c r="A5" s="184" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="205" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="189" t="s">
+      <c r="C5" s="184" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="194" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="189" t="s">
+      <c r="E5" s="184" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="189" t="s">
+      <c r="F5" s="184" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="189" t="s">
+      <c r="G5" s="184" t="s">
         <v>22</v>
       </c>
       <c r="H5" s="191" t="s">
@@ -3936,37 +3936,37 @@
       <c r="I5" s="194" t="s">
         <v>81</v>
       </c>
-      <c r="J5" s="187" t="s">
+      <c r="J5" s="189" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="189" t="s">
         <v>58</v>
       </c>
-      <c r="L5" s="187" t="s">
+      <c r="L5" s="189" t="s">
         <v>114</v>
       </c>
-      <c r="M5" s="187" t="s">
+      <c r="M5" s="189" t="s">
         <v>116</v>
       </c>
-      <c r="N5" s="187" t="s">
+      <c r="N5" s="189" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="190"/>
+      <c r="A6" s="185"/>
       <c r="B6" s="206"/>
-      <c r="C6" s="190"/>
+      <c r="C6" s="185"/>
       <c r="D6" s="207"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="185"/>
+      <c r="G6" s="185"/>
       <c r="H6" s="192"/>
       <c r="I6" s="195"/>
       <c r="J6" s="193"/>
-      <c r="K6" s="188"/>
+      <c r="K6" s="190"/>
       <c r="L6" s="193"/>
-      <c r="M6" s="188"/>
-      <c r="N6" s="188"/>
+      <c r="M6" s="190"/>
+      <c r="N6" s="190"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
@@ -6051,32 +6051,32 @@
       </c>
     </row>
     <row r="54" spans="1:16" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C54" s="184"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
-      <c r="F54" s="184"/>
-      <c r="G54" s="184"/>
-      <c r="H54" s="184"/>
-      <c r="I54" s="184"/>
-      <c r="J54" s="184"/>
-      <c r="K54" s="184"/>
-      <c r="L54" s="184"/>
-      <c r="M54" s="184"/>
-      <c r="N54" s="184"/>
+      <c r="C54" s="186"/>
+      <c r="D54" s="186"/>
+      <c r="E54" s="186"/>
+      <c r="F54" s="186"/>
+      <c r="G54" s="186"/>
+      <c r="H54" s="186"/>
+      <c r="I54" s="186"/>
+      <c r="J54" s="186"/>
+      <c r="K54" s="186"/>
+      <c r="L54" s="186"/>
+      <c r="M54" s="186"/>
+      <c r="N54" s="186"/>
     </row>
     <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C55" s="184"/>
-      <c r="D55" s="184"/>
-      <c r="E55" s="184"/>
-      <c r="F55" s="184"/>
-      <c r="G55" s="184"/>
-      <c r="H55" s="184"/>
-      <c r="I55" s="184"/>
-      <c r="J55" s="184"/>
-      <c r="K55" s="184"/>
-      <c r="L55" s="184"/>
-      <c r="M55" s="184"/>
-      <c r="N55" s="184"/>
+      <c r="C55" s="186"/>
+      <c r="D55" s="186"/>
+      <c r="E55" s="186"/>
+      <c r="F55" s="186"/>
+      <c r="G55" s="186"/>
+      <c r="H55" s="186"/>
+      <c r="I55" s="186"/>
+      <c r="J55" s="186"/>
+      <c r="K55" s="186"/>
+      <c r="L55" s="186"/>
+      <c r="M55" s="186"/>
+      <c r="N55" s="186"/>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="C56" s="70"/>
@@ -6093,107 +6093,109 @@
       <c r="N56" s="70"/>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C57" s="184" t="s">
+      <c r="C57" s="186" t="s">
         <v>99</v>
       </c>
-      <c r="D57" s="184"/>
-      <c r="E57" s="184"/>
-      <c r="F57" s="184"/>
-      <c r="G57" s="184"/>
-      <c r="H57" s="184"/>
-      <c r="I57" s="184"/>
-      <c r="J57" s="184"/>
-      <c r="K57" s="184"/>
-      <c r="L57" s="184"/>
-      <c r="M57" s="184"/>
-      <c r="N57" s="184"/>
+      <c r="D57" s="186"/>
+      <c r="E57" s="186"/>
+      <c r="F57" s="186"/>
+      <c r="G57" s="186"/>
+      <c r="H57" s="186"/>
+      <c r="I57" s="186"/>
+      <c r="J57" s="186"/>
+      <c r="K57" s="186"/>
+      <c r="L57" s="186"/>
+      <c r="M57" s="186"/>
+      <c r="N57" s="186"/>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C58" s="184"/>
-      <c r="D58" s="184"/>
-      <c r="E58" s="184"/>
-      <c r="F58" s="184"/>
-      <c r="G58" s="184"/>
-      <c r="H58" s="184"/>
-      <c r="I58" s="184"/>
-      <c r="J58" s="184"/>
-      <c r="K58" s="184"/>
-      <c r="L58" s="184"/>
-      <c r="M58" s="184"/>
-      <c r="N58" s="184"/>
+      <c r="C58" s="186"/>
+      <c r="D58" s="186"/>
+      <c r="E58" s="186"/>
+      <c r="F58" s="186"/>
+      <c r="G58" s="186"/>
+      <c r="H58" s="186"/>
+      <c r="I58" s="186"/>
+      <c r="J58" s="186"/>
+      <c r="K58" s="186"/>
+      <c r="L58" s="186"/>
+      <c r="M58" s="186"/>
+      <c r="N58" s="186"/>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C59" s="184"/>
-      <c r="D59" s="184"/>
-      <c r="E59" s="184"/>
-      <c r="F59" s="184"/>
-      <c r="G59" s="184"/>
-      <c r="H59" s="184"/>
-      <c r="I59" s="184"/>
-      <c r="J59" s="184"/>
-      <c r="K59" s="184"/>
-      <c r="L59" s="184"/>
-      <c r="M59" s="184"/>
-      <c r="N59" s="184"/>
+      <c r="C59" s="186"/>
+      <c r="D59" s="186"/>
+      <c r="E59" s="186"/>
+      <c r="F59" s="186"/>
+      <c r="G59" s="186"/>
+      <c r="H59" s="186"/>
+      <c r="I59" s="186"/>
+      <c r="J59" s="186"/>
+      <c r="K59" s="186"/>
+      <c r="L59" s="186"/>
+      <c r="M59" s="186"/>
+      <c r="N59" s="186"/>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C60" s="184"/>
-      <c r="D60" s="184"/>
-      <c r="E60" s="184"/>
-      <c r="F60" s="184"/>
-      <c r="G60" s="184"/>
-      <c r="H60" s="184"/>
-      <c r="I60" s="184"/>
-      <c r="J60" s="184"/>
-      <c r="K60" s="184"/>
-      <c r="L60" s="184"/>
-      <c r="M60" s="184"/>
-      <c r="N60" s="184"/>
+      <c r="C60" s="186"/>
+      <c r="D60" s="186"/>
+      <c r="E60" s="186"/>
+      <c r="F60" s="186"/>
+      <c r="G60" s="186"/>
+      <c r="H60" s="186"/>
+      <c r="I60" s="186"/>
+      <c r="J60" s="186"/>
+      <c r="K60" s="186"/>
+      <c r="L60" s="186"/>
+      <c r="M60" s="186"/>
+      <c r="N60" s="186"/>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C61" s="184"/>
-      <c r="D61" s="184"/>
-      <c r="E61" s="184"/>
-      <c r="F61" s="184"/>
-      <c r="G61" s="184"/>
-      <c r="H61" s="184"/>
-      <c r="I61" s="184"/>
-      <c r="J61" s="184"/>
-      <c r="K61" s="184"/>
-      <c r="L61" s="184"/>
-      <c r="M61" s="184"/>
-      <c r="N61" s="184"/>
+      <c r="C61" s="186"/>
+      <c r="D61" s="186"/>
+      <c r="E61" s="186"/>
+      <c r="F61" s="186"/>
+      <c r="G61" s="186"/>
+      <c r="H61" s="186"/>
+      <c r="I61" s="186"/>
+      <c r="J61" s="186"/>
+      <c r="K61" s="186"/>
+      <c r="L61" s="186"/>
+      <c r="M61" s="186"/>
+      <c r="N61" s="186"/>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C62" s="184"/>
-      <c r="D62" s="184"/>
-      <c r="E62" s="184"/>
-      <c r="F62" s="184"/>
-      <c r="G62" s="184"/>
-      <c r="H62" s="184"/>
-      <c r="I62" s="184"/>
-      <c r="J62" s="184"/>
-      <c r="K62" s="184"/>
-      <c r="L62" s="184"/>
-      <c r="M62" s="184"/>
-      <c r="N62" s="184"/>
+      <c r="C62" s="186"/>
+      <c r="D62" s="186"/>
+      <c r="E62" s="186"/>
+      <c r="F62" s="186"/>
+      <c r="G62" s="186"/>
+      <c r="H62" s="186"/>
+      <c r="I62" s="186"/>
+      <c r="J62" s="186"/>
+      <c r="K62" s="186"/>
+      <c r="L62" s="186"/>
+      <c r="M62" s="186"/>
+      <c r="N62" s="186"/>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="C63" s="184"/>
-      <c r="D63" s="184"/>
-      <c r="E63" s="184"/>
-      <c r="F63" s="184"/>
-      <c r="G63" s="184"/>
-      <c r="H63" s="184"/>
-      <c r="I63" s="184"/>
-      <c r="J63" s="184"/>
-      <c r="K63" s="184"/>
-      <c r="L63" s="184"/>
-      <c r="M63" s="184"/>
-      <c r="N63" s="184"/>
+      <c r="C63" s="186"/>
+      <c r="D63" s="186"/>
+      <c r="E63" s="186"/>
+      <c r="F63" s="186"/>
+      <c r="G63" s="186"/>
+      <c r="H63" s="186"/>
+      <c r="I63" s="186"/>
+      <c r="J63" s="186"/>
+      <c r="K63" s="186"/>
+      <c r="L63" s="186"/>
+      <c r="M63" s="186"/>
+      <c r="N63" s="186"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="D5:D6"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="C57:N63"/>
@@ -6210,8 +6212,6 @@
     <mergeCell ref="A1:J4"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
